--- a/results/ncbc_s13/norm/reference_waveforms_R.xlsx
+++ b/results/ncbc_s13/norm/reference_waveforms_R.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,625 +417,377 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>step_1</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>step_2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>step_3</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>step_4</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>step_5</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>step_6</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>step_7</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>step_8</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>step_9</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>step_10</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>step_11</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>step_12</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>step_13</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>step_14</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>step_15</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>step_16</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>step_17</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>step_18</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>step_19</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>step_20</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>step_21</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>step_22</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>step_23</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>step_24</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>step_25</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>step_26</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>step_27</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>step_28</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>step_29</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>step_30</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>step_31</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>step_32</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>step_33</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>step_34</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>step_35</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_36</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>step_37</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>step_38</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>step_39</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>step_40</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>step_41</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>step_42</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_43</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>step_44</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>step_45</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>step_46</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>step_47</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>step_48</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>step_49</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>step_50</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>step_51</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_52</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>step_53</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>step_54</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>step_55</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>step_56</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>step_57</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>step_58</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>step_59</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>step_60</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>step_61</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_62</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>step_63</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>step_64</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>step_65</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>step_66</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>step_67</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>step_68</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_69</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>step_70</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>step_71</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>step_72</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>step_73</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>step_74</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>step_75</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>step_76</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>step_77</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_78</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>step_79</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>step_80</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>step_81</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>step_82</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>step_83</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>step_84</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>step_85</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>step_86</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>step_87</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_88</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>step_89</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>step_90</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>step_91</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>step_92</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>step_93</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>step_94</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_95</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>step_96</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>step_97</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>step_98</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>step_99</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>step_100</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>step_101</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>step_102</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>step_103</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_104</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>step_105</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>step_106</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>step_107</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>step_108</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>step_109</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>step_110</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>step_111</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>step_112</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>step_113</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_114</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>step_115</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>step_116</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>step_117</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>step_118</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>step_119</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>step_120</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_121</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>step_122</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>step_123</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>step_124</t>
-        </is>
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O1" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V1" t="n">
+        <v>21</v>
+      </c>
+      <c r="W1" t="n">
+        <v>22</v>
+      </c>
+      <c r="X1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="n">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="n">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="n">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="n">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="n">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="n">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="n">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="n">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="n">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="n">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="n">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="n">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="n">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="n">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="n">
+        <v>80</v>
+      </c>
+      <c r="CD1" t="n">
+        <v>81</v>
+      </c>
+      <c r="CE1" t="n">
+        <v>82</v>
+      </c>
+      <c r="CF1" t="n">
+        <v>83</v>
+      </c>
+      <c r="CG1" t="n">
+        <v>84</v>
+      </c>
+      <c r="CH1" t="n">
+        <v>85</v>
+      </c>
+      <c r="CI1" t="n">
+        <v>86</v>
+      </c>
+      <c r="CJ1" t="n">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="n">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="n">
+        <v>89</v>
+      </c>
+      <c r="CM1" t="n">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="n">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="n">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="n">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="n">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="n">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="n">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="n">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="n">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="n">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="n">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="n">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="n">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="n">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="n">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="n">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="n">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="n">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="n">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="n">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="n">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="n">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="n">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="n">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="n">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="n">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="n">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="n">
+        <v>117</v>
+      </c>
+      <c r="DO1" t="n">
+        <v>118</v>
+      </c>
+      <c r="DP1" t="n">
+        <v>119</v>
+      </c>
+      <c r="DQ1" t="n">
+        <v>120</v>
+      </c>
+      <c r="DR1" t="n">
+        <v>121</v>
+      </c>
+      <c r="DS1" t="n">
+        <v>122</v>
+      </c>
+      <c r="DT1" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="2">
@@ -1486,7 +1226,7 @@
         <v>0.0277017901656359</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01796022346293343</v>
+        <v>0.01796022346293342</v>
       </c>
       <c r="V3" t="n">
         <v>0.02283721036972893</v>
@@ -1561,7 +1301,7 @@
         <v>0.01728312101964595</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.03383530153778781</v>
+        <v>0.03383530153778782</v>
       </c>
       <c r="AU3" t="n">
         <v>0.01754370291059334</v>
@@ -1576,7 +1316,7 @@
         <v>0.01841406557698505</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.06616471648581486</v>
+        <v>0.06616471648581485</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.02307696435252547</v>
@@ -1800,13 +1540,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1949062247683468</v>
+        <v>0.1949062247683467</v>
       </c>
       <c r="B4" t="n">
         <v>0.0733728547943297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0825867137605846</v>
+        <v>0.08258671376058459</v>
       </c>
       <c r="D4" t="n">
         <v>0.03406905923820813</v>
@@ -1824,10 +1564,10 @@
         <v>0.04449363976757113</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04610725319678441</v>
+        <v>0.04610725319678442</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0473145408768933</v>
+        <v>0.04731454087689329</v>
       </c>
       <c r="K4" t="n">
         <v>0.04916899700444299</v>
@@ -1854,7 +1594,7 @@
         <v>0.0686116085372922</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04555966381557424</v>
+        <v>0.04555966381557425</v>
       </c>
       <c r="T4" t="n">
         <v>0.06672567018081285</v>
@@ -1890,7 +1630,7 @@
         <v>0.05835143545705335</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.05789356733299261</v>
+        <v>0.05789356733299263</v>
       </c>
       <c r="AF4" t="n">
         <v>0.05062528025987546</v>
@@ -1914,7 +1654,7 @@
         <v>0.08146135739710657</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08648816841977067</v>
+        <v>0.08648816841977065</v>
       </c>
       <c r="AN4" t="n">
         <v>0.08303979176992463</v>
@@ -1944,7 +1684,7 @@
         <v>0.08026313779122916</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.04556654691798481</v>
+        <v>0.04556654691798482</v>
       </c>
       <c r="AX4" t="n">
         <v>0.06677662782271597</v>
@@ -2001,16 +1741,16 @@
         <v>0.06893899447019618</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.05620239783126493</v>
+        <v>0.05620239783126494</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.06278179251768881</v>
+        <v>0.0627817925176888</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0770557086553072</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.08067534357140246</v>
+        <v>0.08067534357140245</v>
       </c>
       <c r="BT4" t="n">
         <v>0.04732371933133121</v>
@@ -2052,10 +1792,10 @@
         <v>0.05191702213457618</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0622519606458411</v>
+        <v>0.06225196064584109</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.07421195949305685</v>
+        <v>0.07421195949305684</v>
       </c>
       <c r="CI4" t="n">
         <v>0.08454165349907307</v>
@@ -2133,7 +1873,7 @@
         <v>0.06526360902026417</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.1198977084291105</v>
+        <v>0.1198977084291106</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05133667832420916</v>
@@ -2145,7 +1885,7 @@
         <v>0.1034451318042739</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.06823325411596559</v>
+        <v>0.06823325411596558</v>
       </c>
       <c r="DM4" t="n">
         <v>0.0477890950777345</v>
@@ -2204,7 +1944,7 @@
         <v>0.0905294390681847</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09764476240771348</v>
+        <v>0.09764476240771347</v>
       </c>
       <c r="L5" t="n">
         <v>0.116603911156344</v>
@@ -2234,7 +1974,7 @@
         <v>0.1278869833976816</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1071363158994597</v>
+        <v>0.1071363158994598</v>
       </c>
       <c r="V5" t="n">
         <v>0.1492352064123122</v>
@@ -2405,7 +2145,7 @@
         <v>0.1115304312924184</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1306096997375364</v>
+        <v>0.1306096997375365</v>
       </c>
       <c r="CA5" t="n">
         <v>0.1258803275019244</v>
@@ -2507,7 +2247,7 @@
         <v>0.1410032064080288</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.231156958697577</v>
+        <v>0.2311569586975769</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1016044127956966</v>
@@ -2659,7 +2399,7 @@
         <v>0.1884575899270452</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2626421634968486</v>
+        <v>0.2626421634968485</v>
       </c>
       <c r="AM6" t="n">
         <v>0.2474903596141058</v>
@@ -2671,7 +2411,7 @@
         <v>0.233388252134773</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.28076378151697</v>
+        <v>0.2807637815169701</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.2246787999147932</v>
@@ -3189,7 +2929,7 @@
         <v>0.3514830143087516</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.4522225885524272</v>
+        <v>0.4522225885524271</v>
       </c>
       <c r="CM7" t="n">
         <v>0.3625166732162898</v>
@@ -3198,7 +2938,7 @@
         <v>0.3754619024225433</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.3403144754480477</v>
+        <v>0.3403144754480476</v>
       </c>
       <c r="CP7" t="n">
         <v>0.3971528156961546</v>
@@ -3219,7 +2959,7 @@
         <v>0.4155467690793461</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.3745397526575985</v>
+        <v>0.3745397526575986</v>
       </c>
       <c r="CW7" t="n">
         <v>0.2845596770364263</v>
@@ -3228,7 +2968,7 @@
         <v>0.4009181482988789</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.3725108098725862</v>
+        <v>0.3725108098725861</v>
       </c>
       <c r="CZ7" t="n">
         <v>0.372171786583868</v>
@@ -3273,7 +3013,7 @@
         <v>0.3225388569135085</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.3628035831208704</v>
+        <v>0.3628035831208703</v>
       </c>
       <c r="DO7" t="n">
         <v>0.4261664251973273</v>
@@ -3299,7 +3039,7 @@
         <v>0.6246343436573791</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2267955413113997</v>
+        <v>0.2267955413113996</v>
       </c>
       <c r="C8" t="n">
         <v>0.2982746199313919</v>
@@ -3425,7 +3165,7 @@
         <v>0.4472968474191775</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.3682562543780718</v>
+        <v>0.3682562543780719</v>
       </c>
       <c r="AS8" t="n">
         <v>0.4557280085487477</v>
@@ -3434,7 +3174,7 @@
         <v>0.4848104358716383</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3979888248706722</v>
+        <v>0.3979888248706721</v>
       </c>
       <c r="AV8" t="n">
         <v>0.4994560297495816</v>
@@ -3446,13 +3186,13 @@
         <v>0.5908146144001564</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5642296827912912</v>
+        <v>0.564229682791291</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.5465912006735278</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.6905873588091072</v>
+        <v>0.690587358809107</v>
       </c>
       <c r="BB8" t="n">
         <v>0.4443350292850833</v>
@@ -3479,7 +3219,7 @@
         <v>0.3126170993062694</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4790550184351132</v>
+        <v>0.4790550184351133</v>
       </c>
       <c r="BK8" t="n">
         <v>0.7247526039626507</v>
@@ -3506,7 +3246,7 @@
         <v>0.4553533519839388</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.4830838945570352</v>
+        <v>0.4830838945570353</v>
       </c>
       <c r="BT8" t="n">
         <v>0.344820246564457</v>
@@ -3560,13 +3300,13 @@
         <v>0.4680962018422217</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.4766222712558269</v>
+        <v>0.4766222712558268</v>
       </c>
       <c r="CL8" t="n">
         <v>0.5953953591212031</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.4819093493196048</v>
+        <v>0.4819093493196047</v>
       </c>
       <c r="CN8" t="n">
         <v>0.5251389304871946</v>
@@ -3578,13 +3318,13 @@
         <v>0.5339806276640213</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.4250376371231667</v>
+        <v>0.4250376371231668</v>
       </c>
       <c r="CR8" t="n">
         <v>0.530247810414436</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.6000636022132466</v>
+        <v>0.6000636022132467</v>
       </c>
       <c r="CT8" t="n">
         <v>0.5963016668788167</v>
@@ -3617,7 +3357,7 @@
         <v>0.5328185695417152</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.5016573974687761</v>
+        <v>0.5016573974687762</v>
       </c>
       <c r="DE8" t="n">
         <v>0.5740080307710974</v>
@@ -3685,7 +3425,7 @@
         <v>0.2662766701788664</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4031994084657608</v>
+        <v>0.4031994084657609</v>
       </c>
       <c r="G9" t="n">
         <v>0.3424981199927788</v>
@@ -3694,7 +3434,7 @@
         <v>0.5771179232125232</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5329220311500744</v>
+        <v>0.5329220311500743</v>
       </c>
       <c r="J9" t="n">
         <v>0.4588868943592823</v>
@@ -3742,13 +3482,13 @@
         <v>0.663365876208809</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5579783138607854</v>
+        <v>0.5579783138607856</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6333482257765863</v>
+        <v>0.6333482257765864</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6095562364942558</v>
+        <v>0.6095562364942559</v>
       </c>
       <c r="AB9" t="n">
         <v>0.746174584844417</v>
@@ -3775,10 +3515,10 @@
         <v>0.7175974564192652</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.6915455028245444</v>
+        <v>0.6915455028245443</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.5714412320757337</v>
+        <v>0.5714412320757338</v>
       </c>
       <c r="AL9" t="n">
         <v>0.6575301745936861</v>
@@ -3805,7 +3545,7 @@
         <v>0.5919850430617394</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.6165702169301193</v>
+        <v>0.6165702169301194</v>
       </c>
       <c r="AU9" t="n">
         <v>0.5323848136142147</v>
@@ -3841,7 +3581,7 @@
         <v>0.5864479655730401</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.5793359619129539</v>
+        <v>0.579335961912954</v>
       </c>
       <c r="BG9" t="n">
         <v>0.4865475237740102</v>
@@ -3868,13 +3608,13 @@
         <v>0.6344397872253866</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.6084802633276745</v>
+        <v>0.6084802633276746</v>
       </c>
       <c r="BP9" t="n">
         <v>0.6576627695252156</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.6473735907905473</v>
+        <v>0.6473735907905475</v>
       </c>
       <c r="BR9" t="n">
         <v>0.5905883993760128</v>
@@ -3898,7 +3638,7 @@
         <v>0.5832807891801262</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.5069958259703021</v>
+        <v>0.506995825970302</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.5842304942392347</v>
@@ -3907,7 +3647,7 @@
         <v>0.6128887105563922</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.5997648655697873</v>
+        <v>0.5997648655697871</v>
       </c>
       <c r="CC9" t="n">
         <v>0.5648660320153135</v>
@@ -3955,7 +3695,7 @@
         <v>0.5493383499676422</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.6664659904911685</v>
+        <v>0.6664659904911684</v>
       </c>
       <c r="CS9" t="n">
         <v>0.7460970753913114</v>
@@ -3973,7 +3713,7 @@
         <v>0.5544275863022861</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.6893998929963686</v>
+        <v>0.6893998929963687</v>
       </c>
       <c r="CY9" t="n">
         <v>0.6164989705608395</v>
@@ -3994,7 +3734,7 @@
         <v>0.6352205564420196</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.7064630884330296</v>
+        <v>0.7064630884330295</v>
       </c>
       <c r="DF9" t="n">
         <v>0.6017122425084882</v>
@@ -4056,7 +3796,7 @@
         <v>0.2994832126020048</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3453898517195529</v>
+        <v>0.3453898517195531</v>
       </c>
       <c r="F10" t="n">
         <v>0.5164901504970305</v>
@@ -4080,7 +3820,7 @@
         <v>0.6836613881937504</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7676833030969755</v>
+        <v>0.7676833030969756</v>
       </c>
       <c r="N10" t="n">
         <v>0.5943637691570237</v>
@@ -4089,7 +3829,7 @@
         <v>0.7239409103218608</v>
       </c>
       <c r="P10" t="n">
-        <v>0.849922735206861</v>
+        <v>0.8499227352068608</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5862315025517616</v>
@@ -4104,7 +3844,7 @@
         <v>0.684757857350543</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7818197230375462</v>
+        <v>0.7818197230375463</v>
       </c>
       <c r="V10" t="n">
         <v>0.8581774484501403</v>
@@ -4113,7 +3853,7 @@
         <v>0.9319944692204197</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8014239222198365</v>
+        <v>0.8014239222198367</v>
       </c>
       <c r="Y10" t="n">
         <v>0.6885147078926136</v>
@@ -4158,7 +3898,7 @@
         <v>0.7834701953290855</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.7569748340471708</v>
+        <v>0.7569748340471707</v>
       </c>
       <c r="AN10" t="n">
         <v>0.7904680452415752</v>
@@ -4179,7 +3919,7 @@
         <v>0.7217256566771977</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.7399718589897857</v>
+        <v>0.7399718589897855</v>
       </c>
       <c r="AU10" t="n">
         <v>0.6702130573778569</v>
@@ -4194,7 +3934,7 @@
         <v>0.884665804993259</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.8033468170344202</v>
+        <v>0.80334681703442</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.8303169150678239</v>
@@ -4203,7 +3943,7 @@
         <v>0.9652371531533354</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.7300792740381753</v>
+        <v>0.7300792740381754</v>
       </c>
       <c r="BC10" t="n">
         <v>0.9031541161280539</v>
@@ -4284,7 +4024,7 @@
         <v>0.7277257081482934</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.6865880994684463</v>
+        <v>0.6865880994684465</v>
       </c>
       <c r="CD10" t="n">
         <v>0.6680529288408982</v>
@@ -4380,7 +4120,7 @@
         <v>0.9082488189401732</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.5776311028703401</v>
+        <v>0.57763110287034</v>
       </c>
       <c r="DJ10" t="n">
         <v>0.9487369388982244</v>
@@ -4439,7 +4179,7 @@
         <v>0.5750717646138211</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8552718587690867</v>
+        <v>0.8552718587690866</v>
       </c>
       <c r="I11" t="n">
         <v>0.813579864985815</v>
@@ -4460,13 +4200,13 @@
         <v>0.7293630036125622</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8357117106106631</v>
+        <v>0.835711710610663</v>
       </c>
       <c r="P11" t="n">
         <v>0.9706718948892956</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7045180530239535</v>
+        <v>0.7045180530239534</v>
       </c>
       <c r="R11" t="n">
         <v>0.8475038316818573</v>
@@ -4589,10 +4329,10 @@
         <v>0.8780206006247516</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.8235286702312666</v>
+        <v>0.8235286702312665</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.7454793047745515</v>
+        <v>0.7454793047745517</v>
       </c>
       <c r="BH11" t="n">
         <v>0.9223932491482759</v>
@@ -4628,7 +4368,7 @@
         <v>0.8497295621037022</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.8471747768150616</v>
+        <v>0.8471747768150617</v>
       </c>
       <c r="BT11" t="n">
         <v>0.6957997534580468</v>
@@ -4664,7 +4404,7 @@
         <v>0.7807229567445011</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.8887253265477906</v>
+        <v>0.8887253265477905</v>
       </c>
       <c r="CF11" t="n">
         <v>0.8083122045499559</v>
@@ -4682,7 +4422,7 @@
         <v>0.8195194963215671</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.8360886598549312</v>
+        <v>0.8360886598549313</v>
       </c>
       <c r="CL11" t="n">
         <v>0.9482555175894606</v>
@@ -4736,7 +4476,7 @@
         <v>1.018936332282119</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.8930212020957</v>
+        <v>0.8930212020957002</v>
       </c>
       <c r="DD11" t="n">
         <v>0.8585463647240057</v>
@@ -4798,7 +4538,7 @@
         <v>0.4218259811128828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5702999107118126</v>
+        <v>0.5702999107118127</v>
       </c>
       <c r="D12" t="n">
         <v>0.4620149889758262</v>
@@ -4807,7 +4547,7 @@
         <v>0.5268019938929334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7394843359779786</v>
+        <v>0.7394843359779785</v>
       </c>
       <c r="G12" t="n">
         <v>0.6980644422742027</v>
@@ -4888,7 +4628,7 @@
         <v>0.9400390392792506</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.0117108459657</v>
+        <v>1.011710845965701</v>
       </c>
       <c r="AH12" t="n">
         <v>0.959105615415053</v>
@@ -4897,7 +4637,7 @@
         <v>0.9244390405075565</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.945801353625366</v>
+        <v>0.9458013536253661</v>
       </c>
       <c r="AK12" t="n">
         <v>0.9314691122892882</v>
@@ -4909,7 +4649,7 @@
         <v>0.9575379502946798</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.977709661510796</v>
+        <v>0.9777096615107961</v>
       </c>
       <c r="AO12" t="n">
         <v>0.8971988458247228</v>
@@ -4924,7 +4664,7 @@
         <v>0.8619773939214892</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.9250660636958394</v>
+        <v>0.9250660636958395</v>
       </c>
       <c r="AT12" t="n">
         <v>0.9272826243728561</v>
@@ -4936,7 +4676,7 @@
         <v>1.000648767228868</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.9924948185874405</v>
+        <v>0.9924948185874406</v>
       </c>
       <c r="AX12" t="n">
         <v>1.061237166479608</v>
@@ -5035,7 +4775,7 @@
         <v>0.8748579387843508</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.877640637752288</v>
+        <v>0.8776406377522882</v>
       </c>
       <c r="CE12" t="n">
         <v>0.9596635246708674</v>
@@ -5056,7 +4796,7 @@
         <v>0.9027896410870629</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.9161856825777652</v>
+        <v>0.916185682577765</v>
       </c>
       <c r="CL12" t="n">
         <v>1.013936479636977</v>
@@ -5077,7 +4817,7 @@
         <v>0.8547268787163623</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.9502921560841411</v>
+        <v>0.9502921560841412</v>
       </c>
       <c r="CS12" t="n">
         <v>1.036652773333924</v>
@@ -5092,10 +4832,10 @@
         <v>0.9946429630328597</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.941043047178898</v>
+        <v>0.9410430471788981</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.01030731600182</v>
+        <v>1.010307316001819</v>
       </c>
       <c r="CY12" t="n">
         <v>0.8993840167215598</v>
@@ -5158,7 +4898,7 @@
         <v>0.5942671376611423</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.353744118094305</v>
+        <v>0.3537441180943049</v>
       </c>
       <c r="DT12" t="n">
         <v>0.4509869568073342</v>
@@ -5166,7 +4906,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.7343280801318637</v>
+        <v>0.7343280801318635</v>
       </c>
       <c r="B13" t="n">
         <v>0.4658379906552211</v>
@@ -5205,7 +4945,7 @@
         <v>1.089623335968827</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9543246141829954</v>
+        <v>0.9543246141829953</v>
       </c>
       <c r="O13" t="n">
         <v>0.9950850663898424</v>
@@ -5217,7 +4957,7 @@
         <v>0.8908629218353924</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9983789444178243</v>
+        <v>0.9983789444178242</v>
       </c>
       <c r="S13" t="n">
         <v>1.084329241875415</v>
@@ -5358,13 +5098,13 @@
         <v>1.027547026785086</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.9688113223106852</v>
+        <v>0.9688113223106853</v>
       </c>
       <c r="BN13" t="n">
         <v>1.036369167546843</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9947444620842982</v>
+        <v>0.9947444620842981</v>
       </c>
       <c r="BP13" t="n">
         <v>1.075945032532954</v>
@@ -5409,7 +5149,7 @@
         <v>0.9308259771993361</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.9558581817086</v>
+        <v>0.9558581817085999</v>
       </c>
       <c r="CE13" t="n">
         <v>1.004858056828335</v>
@@ -5552,7 +5292,7 @@
         <v>0.6101367822146901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6897093437824443</v>
+        <v>0.6897093437824441</v>
       </c>
       <c r="F14" t="n">
         <v>0.9069995787641089</v>
@@ -5612,7 +5352,7 @@
         <v>1.094831943069353</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.039403750088698</v>
+        <v>1.039403750088697</v>
       </c>
       <c r="Z14" t="n">
         <v>1.05525939542823</v>
@@ -5624,7 +5364,7 @@
         <v>1.085023060888748</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.050135426039943</v>
+        <v>1.050135426039944</v>
       </c>
       <c r="AD14" t="n">
         <v>0.9922142070618062</v>
@@ -5876,7 +5616,7 @@
         <v>1.071462636041788</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.9657750725574494</v>
+        <v>0.9657750725574492</v>
       </c>
       <c r="DJ14" t="n">
         <v>1.094892452252099</v>
@@ -5909,7 +5649,7 @@
         <v>0.4804745559070704</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.5827000195865409</v>
+        <v>0.5827000195865408</v>
       </c>
     </row>
     <row r="15">
@@ -5929,7 +5669,7 @@
         <v>0.7514248746510396</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9629569887711045</v>
+        <v>0.9629569887711046</v>
       </c>
       <c r="G15" t="n">
         <v>0.9692889138914077</v>
@@ -5941,7 +5681,7 @@
         <v>1.094401291793737</v>
       </c>
       <c r="J15" t="n">
-        <v>1.100296579757003</v>
+        <v>1.100296579757002</v>
       </c>
       <c r="K15" t="n">
         <v>1.074502582218082</v>
@@ -6010,7 +5750,7 @@
         <v>1.074513886697952</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.116479101780728</v>
+        <v>1.116479101780729</v>
       </c>
       <c r="AH15" t="n">
         <v>1.047705455849372</v>
@@ -6294,7 +6034,7 @@
         <v>0.5882971493757568</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6729706332158595</v>
+        <v>0.6729706332158594</v>
       </c>
       <c r="D16" t="n">
         <v>0.7068610579853026</v>
@@ -6405,7 +6145,7 @@
         <v>1.080267406081492</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.089427853138651</v>
+        <v>1.08942785313865</v>
       </c>
       <c r="AO16" t="n">
         <v>1.063249653533548</v>
@@ -6447,7 +6187,7 @@
         <v>1.138771545949776</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.083527867751634</v>
+        <v>1.083527867751633</v>
       </c>
       <c r="BC16" t="n">
         <v>1.06308299302713</v>
@@ -6465,7 +6205,7 @@
         <v>1.062946725818221</v>
       </c>
       <c r="BH16" t="n">
-        <v>1.13176056339738</v>
+        <v>1.131760563397381</v>
       </c>
       <c r="BI16" t="n">
         <v>0.5367617402139585</v>
@@ -6570,7 +6310,7 @@
         <v>1.094199017247965</v>
       </c>
       <c r="CQ16" t="n">
-        <v>1.034811275480438</v>
+        <v>1.034811275480439</v>
       </c>
       <c r="CR16" t="n">
         <v>1.044877944801105</v>
@@ -6648,10 +6388,10 @@
         <v>1.067832362776046</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.799394416224151</v>
+        <v>0.7993944162241511</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.7956560373446198</v>
+        <v>0.7956560373446199</v>
       </c>
       <c r="DS16" t="n">
         <v>0.573040985223924</v>
@@ -6674,7 +6414,7 @@
         <v>0.7378293921845313</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8349976541459795</v>
+        <v>0.8349976541459797</v>
       </c>
       <c r="F17" t="n">
         <v>1.029162704407246</v>
@@ -6854,7 +6594,7 @@
         <v>1.10503415372916</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.055222014288668</v>
+        <v>1.055222014288669</v>
       </c>
       <c r="BN17" t="n">
         <v>1.108453646691004</v>
@@ -6932,7 +6672,7 @@
         <v>1.075866946082306</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.042449549558234</v>
+        <v>1.042449549558233</v>
       </c>
       <c r="CN17" t="n">
         <v>1.108066683775308</v>
@@ -7174,7 +6914,7 @@
         <v>1.080665695662337</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.110949898282834</v>
+        <v>1.110949898282833</v>
       </c>
       <c r="AV18" t="n">
         <v>1.136736788109742</v>
@@ -7216,7 +6956,7 @@
         <v>1.103197806954693</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.761872621548623</v>
+        <v>0.7618726215486228</v>
       </c>
       <c r="BJ18" t="n">
         <v>1.069178363194665</v>
@@ -7515,7 +7255,7 @@
         <v>1.047590309805175</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.058297875503198</v>
+        <v>1.058297875503197</v>
       </c>
       <c r="AK19" t="n">
         <v>1.103257234002948</v>
@@ -7722,7 +7462,7 @@
         <v>1.070479700965447</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.075445270827531</v>
+        <v>1.07544527082753</v>
       </c>
       <c r="DB19" t="n">
         <v>1.047051541500104</v>
@@ -7767,7 +7507,7 @@
         <v>1.066962227432653</v>
       </c>
       <c r="DP19" t="n">
-        <v>1.06763444231477</v>
+        <v>1.067634442314771</v>
       </c>
       <c r="DQ19" t="n">
         <v>0.8922572482517919</v>
@@ -7779,12 +7519,12 @@
         <v>0.6328746677128173</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.7418173172777518</v>
+        <v>0.7418173172777517</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.8949762048643468</v>
+        <v>0.894976204864347</v>
       </c>
       <c r="B20" t="n">
         <v>0.7088772460782642</v>
@@ -7796,7 +7536,7 @@
         <v>0.8085644237649886</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8974825330903857</v>
+        <v>0.8974825330903858</v>
       </c>
       <c r="F20" t="n">
         <v>1.05061824104568</v>
@@ -7835,7 +7575,7 @@
         <v>1.014424241317474</v>
       </c>
       <c r="R20" t="n">
-        <v>1.064617533490707</v>
+        <v>1.064617533490706</v>
       </c>
       <c r="S20" t="n">
         <v>1.065323054628366</v>
@@ -7979,7 +7719,7 @@
         <v>1.024799808650315</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.058676534068737</v>
+        <v>1.058676534068738</v>
       </c>
       <c r="BO20" t="n">
         <v>1.030883283951672</v>
@@ -8114,7 +7854,7 @@
         <v>1.030869424090067</v>
       </c>
       <c r="DG20" t="n">
-        <v>1.060295503502995</v>
+        <v>1.060295503502994</v>
       </c>
       <c r="DH20" t="n">
         <v>0.9964703250695698</v>
@@ -8141,7 +7881,7 @@
         <v>1.037640098503192</v>
       </c>
       <c r="DP20" t="n">
-        <v>1.05475040243812</v>
+        <v>1.054750402438119</v>
       </c>
       <c r="DQ20" t="n">
         <v>0.920191577194906</v>
@@ -8150,7 +7890,7 @@
         <v>0.8759799559970914</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.6414151768020762</v>
+        <v>0.6414151768020763</v>
       </c>
       <c r="DT20" t="n">
         <v>0.7644685772117217</v>
@@ -8179,7 +7919,7 @@
         <v>1.02177550589817</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9845952116222437</v>
+        <v>0.9845952116222436</v>
       </c>
       <c r="I21" t="n">
         <v>1.001339348606748</v>
@@ -8194,7 +7934,7 @@
         <v>1.007958439987334</v>
       </c>
       <c r="M21" t="n">
-        <v>1.031416073448982</v>
+        <v>1.031416073448981</v>
       </c>
       <c r="N21" t="n">
         <v>1.043356057949186</v>
@@ -8248,7 +7988,7 @@
         <v>1.006370166802566</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.014712638607552</v>
+        <v>1.014712638607551</v>
       </c>
       <c r="AF21" t="n">
         <v>1.008506249591532</v>
@@ -8275,7 +8015,7 @@
         <v>0.9844516596226462</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.9969893788227437</v>
+        <v>0.996989378822744</v>
       </c>
       <c r="AO21" t="n">
         <v>1.009298506261125</v>
@@ -8314,7 +8054,7 @@
         <v>1.00512365357209</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.9630930034384155</v>
+        <v>0.9630930034384154</v>
       </c>
       <c r="BB21" t="n">
         <v>0.9872312861688416</v>
@@ -8350,7 +8090,7 @@
         <v>1.030061492712133</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.9935963674523223</v>
+        <v>0.9935963674523224</v>
       </c>
       <c r="BN21" t="n">
         <v>1.021578634025706</v>
@@ -8377,7 +8117,7 @@
         <v>1.009811583427076</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.9778336251368982</v>
+        <v>0.9778336251368981</v>
       </c>
       <c r="BW21" t="n">
         <v>0.9852811130721192</v>
@@ -8410,10 +8150,10 @@
         <v>1.00800011433623</v>
       </c>
       <c r="CG21" t="n">
-        <v>0.9985082193172959</v>
+        <v>0.9985082193172961</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.9944468692619423</v>
+        <v>0.9944468692619424</v>
       </c>
       <c r="CI21" t="n">
         <v>0.9707566302415774</v>
@@ -8431,7 +8171,7 @@
         <v>1.00498490968871</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.016317577428324</v>
+        <v>1.016317577428325</v>
       </c>
       <c r="CO21" t="n">
         <v>0.9973046629961974</v>
@@ -8449,7 +8189,7 @@
         <v>0.9496728944576045</v>
       </c>
       <c r="CT21" t="n">
-        <v>1.002191382722116</v>
+        <v>1.002191382722115</v>
       </c>
       <c r="CU21" t="n">
         <v>1.0050958069969</v>
@@ -8482,7 +8222,7 @@
         <v>1.013676240837091</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.9861041274515979</v>
+        <v>0.9861041274515981</v>
       </c>
       <c r="DF21" t="n">
         <v>1.000365331770551</v>
@@ -8491,13 +8231,13 @@
         <v>1.023785537156984</v>
       </c>
       <c r="DH21" t="n">
-        <v>0.9465325013896332</v>
+        <v>0.9465325013896334</v>
       </c>
       <c r="DI21" t="n">
         <v>1.041577230907454</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.9870351960352179</v>
+        <v>0.9870351960352181</v>
       </c>
       <c r="DK21" t="n">
         <v>0.9729120567050579</v>
@@ -8518,7 +8258,7 @@
         <v>1.03524737180299</v>
       </c>
       <c r="DQ21" t="n">
-        <v>0.944012005779395</v>
+        <v>0.9440120057793951</v>
       </c>
       <c r="DR21" t="n">
         <v>0.9037766766610316</v>
@@ -8583,13 +8323,13 @@
         <v>0.9743098394030943</v>
       </c>
       <c r="R22" t="n">
-        <v>0.980163787942779</v>
+        <v>0.9801637879427789</v>
       </c>
       <c r="S22" t="n">
         <v>0.9839245647123435</v>
       </c>
       <c r="T22" t="n">
-        <v>0.992842801909109</v>
+        <v>0.9928428019091091</v>
       </c>
       <c r="U22" t="n">
         <v>0.9780816356242371</v>
@@ -8598,7 +8338,7 @@
         <v>0.9307534275971161</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9473550604906403</v>
+        <v>0.9473550604906402</v>
       </c>
       <c r="X22" t="n">
         <v>0.9699492887785044</v>
@@ -8616,7 +8356,7 @@
         <v>0.9408422976162223</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.9994252520158411</v>
+        <v>0.999425252015841</v>
       </c>
       <c r="AD22" t="n">
         <v>0.9810939100793602</v>
@@ -8724,7 +8464,7 @@
         <v>0.9886430126002675</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.9551340309963569</v>
+        <v>0.955134030996357</v>
       </c>
       <c r="BN22" t="n">
         <v>0.9763906275166379</v>
@@ -8739,7 +8479,7 @@
         <v>0.9516512671116703</v>
       </c>
       <c r="BR22" t="n">
-        <v>0.9610809547146771</v>
+        <v>0.9610809547146772</v>
       </c>
       <c r="BS22" t="n">
         <v>0.9930835679283979</v>
@@ -8748,7 +8488,7 @@
         <v>0.9890063637370736</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.9709370963500438</v>
+        <v>0.9709370963500437</v>
       </c>
       <c r="BV22" t="n">
         <v>0.937586558558516</v>
@@ -8769,7 +8509,7 @@
         <v>0.9938194545266581</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.9910452866004572</v>
+        <v>0.9910452866004573</v>
       </c>
       <c r="CC22" t="n">
         <v>0.9500420148640913</v>
@@ -8787,13 +8527,13 @@
         <v>0.9751029055514421</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.9577478594885417</v>
+        <v>0.9577478594885416</v>
       </c>
       <c r="CI22" t="n">
         <v>0.9417883964680326</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.9584039183150748</v>
+        <v>0.9584039183150745</v>
       </c>
       <c r="CK22" t="n">
         <v>0.9717596732295818</v>
@@ -8823,7 +8563,7 @@
         <v>0.9148251922770583</v>
       </c>
       <c r="CT22" t="n">
-        <v>0.9511652138107904</v>
+        <v>0.9511652138107906</v>
       </c>
       <c r="CU22" t="n">
         <v>0.9598724500164677</v>
@@ -8838,7 +8578,7 @@
         <v>0.9513946782652546</v>
       </c>
       <c r="CY22" t="n">
-        <v>0.9319826779198767</v>
+        <v>0.9319826779198768</v>
       </c>
       <c r="CZ22" t="n">
         <v>0.9648980603765352</v>
@@ -8859,7 +8599,7 @@
         <v>0.9414642430718387</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.9623126076116967</v>
+        <v>0.9623126076116966</v>
       </c>
       <c r="DG22" t="n">
         <v>0.9801473107516745</v>
@@ -8886,7 +8626,7 @@
         <v>0.9631352189690019</v>
       </c>
       <c r="DO22" t="n">
-        <v>0.9628528363677568</v>
+        <v>0.9628528363677569</v>
       </c>
       <c r="DP22" t="n">
         <v>1.008781814350409</v>
@@ -8954,13 +8694,13 @@
         <v>0.8957228032352976</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9417058597187484</v>
+        <v>0.9417058597187483</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9288119418708871</v>
+        <v>0.928811941870887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9386504316279948</v>
+        <v>0.938650431627995</v>
       </c>
       <c r="T23" t="n">
         <v>0.9465614378777689</v>
@@ -8996,7 +8736,7 @@
         <v>0.9509569921091637</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.9584899073017231</v>
+        <v>0.9584899073017232</v>
       </c>
       <c r="AF23" t="n">
         <v>0.9204142660213469</v>
@@ -9017,10 +8757,10 @@
         <v>0.9518595695345344</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.9068233083947106</v>
+        <v>0.9068233083947107</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.9084111496386632</v>
+        <v>0.9084111496386631</v>
       </c>
       <c r="AN23" t="n">
         <v>0.9093652917244098</v>
@@ -9134,7 +8874,7 @@
         <v>0.9338192839911965</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.959582935952683</v>
+        <v>0.9595829359526828</v>
       </c>
       <c r="BZ23" t="n">
         <v>0.9428314315255898</v>
@@ -9173,7 +8913,7 @@
         <v>0.9378444439675615</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.8809751714283909</v>
+        <v>0.8809751714283907</v>
       </c>
       <c r="CM23" t="n">
         <v>0.9392203184266739</v>
@@ -9182,7 +8922,7 @@
         <v>0.9376916771263306</v>
       </c>
       <c r="CO23" t="n">
-        <v>0.9266684814786186</v>
+        <v>0.9266684814786185</v>
       </c>
       <c r="CP23" t="n">
         <v>0.8928375763333819</v>
@@ -9200,7 +8940,7 @@
         <v>0.8990839908880998</v>
       </c>
       <c r="CU23" t="n">
-        <v>0.9111479066617929</v>
+        <v>0.9111479066617931</v>
       </c>
       <c r="CV23" t="n">
         <v>0.9036575477768307</v>
@@ -9242,7 +8982,7 @@
         <v>0.8396888907110232</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.9701510946169903</v>
+        <v>0.9701510946169902</v>
       </c>
       <c r="DJ23" t="n">
         <v>0.8695359838555939</v>
@@ -9254,7 +8994,7 @@
         <v>0.95145122118012</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.9475467879320423</v>
+        <v>0.9475467879320424</v>
       </c>
       <c r="DN23" t="n">
         <v>0.9210362677128368</v>
@@ -9263,7 +9003,7 @@
         <v>0.920978410352339</v>
       </c>
       <c r="DP23" t="n">
-        <v>0.9756315810089758</v>
+        <v>0.9756315810089757</v>
       </c>
       <c r="DQ23" t="n">
         <v>0.9681563891960873</v>
@@ -9280,7 +9020,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.8845190977373957</v>
+        <v>0.8845190977373958</v>
       </c>
       <c r="B24" t="n">
         <v>0.7589391400675515</v>
@@ -9313,7 +9053,7 @@
         <v>0.9104359613178852</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9021775183984498</v>
+        <v>0.9021775183984497</v>
       </c>
       <c r="M24" t="n">
         <v>0.8636660033658398</v>
@@ -9334,7 +9074,7 @@
         <v>0.8771391911721074</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8922442512987823</v>
+        <v>0.8922442512987822</v>
       </c>
       <c r="T24" t="n">
         <v>0.8969850513425502</v>
@@ -9409,7 +9149,7 @@
         <v>0.8915565689651761</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.926712529580597</v>
+        <v>0.9267125295805969</v>
       </c>
       <c r="AS24" t="n">
         <v>0.9193932731089725</v>
@@ -9418,7 +9158,7 @@
         <v>0.9107882359616696</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.9236997653360691</v>
+        <v>0.9236997653360693</v>
       </c>
       <c r="AV24" t="n">
         <v>0.8653677389064464</v>
@@ -9457,7 +9197,7 @@
         <v>0.9092763266791913</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.8771362857594042</v>
+        <v>0.8771362857594043</v>
       </c>
       <c r="BI24" t="n">
         <v>1.125366044231771</v>
@@ -9517,7 +9257,7 @@
         <v>0.9095364619133857</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.9050756440381916</v>
+        <v>0.9050756440381917</v>
       </c>
       <c r="CC24" t="n">
         <v>0.8897339301438374</v>
@@ -9601,7 +9341,7 @@
         <v>0.8816092720278055</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.8932468301378491</v>
+        <v>0.8932468301378489</v>
       </c>
       <c r="DE24" t="n">
         <v>0.8465748841065178</v>
@@ -9669,7 +9409,7 @@
         <v>0.9017227319249136</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9039514669638241</v>
+        <v>0.903951466963824</v>
       </c>
       <c r="G25" t="n">
         <v>0.8694220429279926</v>
@@ -9699,7 +9439,7 @@
         <v>0.8440811830277326</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7983571193758406</v>
+        <v>0.7983571193758404</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8594968659494269</v>
@@ -9732,7 +9472,7 @@
         <v>0.8317958569234728</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.849827574858298</v>
+        <v>0.8498275748582979</v>
       </c>
       <c r="AB25" t="n">
         <v>0.8087478289409581</v>
@@ -9750,7 +9490,7 @@
         <v>0.829073133134194</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.8640580889077003</v>
+        <v>0.8640580889077002</v>
       </c>
       <c r="AH25" t="n">
         <v>0.848341905293668</v>
@@ -9759,7 +9499,7 @@
         <v>0.8593412931023512</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.8690683065780613</v>
+        <v>0.8690683065780611</v>
       </c>
       <c r="AK25" t="n">
         <v>0.8455015964573261</v>
@@ -9816,7 +9556,7 @@
         <v>0.838101769883803</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.7916421713717674</v>
+        <v>0.7916421713717673</v>
       </c>
       <c r="BD25" t="n">
         <v>0.8663230635689092</v>
@@ -9840,7 +9580,7 @@
         <v>0.8805930539512113</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.8463384871192288</v>
+        <v>0.8463384871192285</v>
       </c>
       <c r="BL25" t="n">
         <v>0.8397517637664131</v>
@@ -9849,7 +9589,7 @@
         <v>0.8245900783029628</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.8286127478982042</v>
+        <v>0.828612747898204</v>
       </c>
       <c r="BO25" t="n">
         <v>0.8627663839499893</v>
@@ -9876,13 +9616,13 @@
         <v>0.8029385913917058</v>
       </c>
       <c r="BW25" t="n">
-        <v>0.8170861052879307</v>
+        <v>0.8170861052879309</v>
       </c>
       <c r="BX25" t="n">
         <v>0.834553812381237</v>
       </c>
       <c r="BY25" t="n">
-        <v>0.8715739743755208</v>
+        <v>0.8715739743755205</v>
       </c>
       <c r="BZ25" t="n">
         <v>0.8485337803695714</v>
@@ -9972,7 +9712,7 @@
         <v>0.7675532007699796</v>
       </c>
       <c r="DC25" t="n">
-        <v>0.8371823886434427</v>
+        <v>0.8371823886434426</v>
       </c>
       <c r="DD25" t="n">
         <v>0.8470853802904185</v>
@@ -10014,7 +9754,7 @@
         <v>0.8956312372816116</v>
       </c>
       <c r="DQ25" t="n">
-        <v>0.9540387944317672</v>
+        <v>0.9540387944317671</v>
       </c>
       <c r="DR25" t="n">
         <v>0.9595711052302985</v>
@@ -10046,7 +9786,7 @@
         <v>0.8585565972009579</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8208438153303177</v>
+        <v>0.8208438153303179</v>
       </c>
       <c r="H26" t="n">
         <v>0.7946526335632069</v>
@@ -10073,7 +9813,7 @@
         <v>0.8015243397681759</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7588138173167894</v>
+        <v>0.7588138173167895</v>
       </c>
       <c r="Q26" t="n">
         <v>0.8175492359126182</v>
@@ -10085,7 +9825,7 @@
         <v>0.803903147577027</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8014745968285448</v>
+        <v>0.8014745968285449</v>
       </c>
       <c r="U26" t="n">
         <v>0.7949864792523111</v>
@@ -10103,7 +9843,7 @@
         <v>0.8018385367718956</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.795904732098359</v>
+        <v>0.7959047320983591</v>
       </c>
       <c r="AA26" t="n">
         <v>0.8076937960860988</v>
@@ -10145,7 +9885,7 @@
         <v>0.800038335875865</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.7832570136005093</v>
+        <v>0.7832570136005091</v>
       </c>
       <c r="AO26" t="n">
         <v>0.7799815773532752</v>
@@ -10190,7 +9930,7 @@
         <v>0.8002874840254094</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.7638204331669148</v>
+        <v>0.7638204331669146</v>
       </c>
       <c r="BD26" t="n">
         <v>0.8265996153393398</v>
@@ -10211,7 +9951,7 @@
         <v>1.102164647468194</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.8431062374230407</v>
+        <v>0.8431062374230406</v>
       </c>
       <c r="BK26" t="n">
         <v>0.8145402416709341</v>
@@ -10226,13 +9966,13 @@
         <v>0.7871662148098909</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.8255778251666366</v>
+        <v>0.8255778251666367</v>
       </c>
       <c r="BP26" t="n">
         <v>0.7946668979405229</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0.8019988617186602</v>
+        <v>0.8019988617186604</v>
       </c>
       <c r="BR26" t="n">
         <v>0.7726635779654227</v>
@@ -10292,7 +10032,7 @@
         <v>0.8033197460253542</v>
       </c>
       <c r="CK26" t="n">
-        <v>0.8190493169795144</v>
+        <v>0.8190493169795143</v>
       </c>
       <c r="CL26" t="n">
         <v>0.7528157103309761</v>
@@ -10343,7 +10083,7 @@
         <v>0.7854849933082794</v>
       </c>
       <c r="DB26" t="n">
-        <v>0.7333728723112141</v>
+        <v>0.733372872311214</v>
       </c>
       <c r="DC26" t="n">
         <v>0.7946839033800354</v>
@@ -10352,7 +10092,7 @@
         <v>0.8029316154855154</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.7635142467284016</v>
+        <v>0.7635142467284017</v>
       </c>
       <c r="DF26" t="n">
         <v>0.779769790779765</v>
@@ -10376,10 +10116,10 @@
         <v>0.8239800162539805</v>
       </c>
       <c r="DM26" t="n">
-        <v>0.8355257541075407</v>
+        <v>0.8355257541075408</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.7853521962379858</v>
+        <v>0.7853521962379857</v>
       </c>
       <c r="DO26" t="n">
         <v>0.7995936267062699</v>
@@ -10397,7 +10137,7 @@
         <v>0.7212307288199323</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.9310273875253245</v>
+        <v>0.9310273875253247</v>
       </c>
     </row>
     <row r="27">
@@ -10429,7 +10169,7 @@
         <v>0.7111702557877934</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7595788910241</v>
+        <v>0.7595788910240998</v>
       </c>
       <c r="K27" t="n">
         <v>0.8053106420342334</v>
@@ -10465,7 +10205,7 @@
         <v>0.7579794761350281</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7188046133294982</v>
+        <v>0.7188046133294981</v>
       </c>
       <c r="W27" t="n">
         <v>0.7064766588265886</v>
@@ -10528,7 +10268,7 @@
         <v>0.7370828463385799</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.7887303269550255</v>
+        <v>0.7887303269550254</v>
       </c>
       <c r="AR27" t="n">
         <v>0.8141074414775391</v>
@@ -10549,7 +10289,7 @@
         <v>0.7916184338117715</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.7572902156604402</v>
+        <v>0.7572902156604403</v>
       </c>
       <c r="AY27" t="n">
         <v>0.760740768938776</v>
@@ -10558,7 +10298,7 @@
         <v>0.7812590302549142</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.7199951451334831</v>
+        <v>0.7199951451334829</v>
       </c>
       <c r="BB27" t="n">
         <v>0.7670590009244912</v>
@@ -10576,7 +10316,7 @@
         <v>0.8148308929367436</v>
       </c>
       <c r="BG27" t="n">
-        <v>0.7780502957006147</v>
+        <v>0.7780502957006146</v>
       </c>
       <c r="BH27" t="n">
         <v>0.747919979512733</v>
@@ -10633,7 +10373,7 @@
         <v>0.7897426927697443</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0.764833787265663</v>
+        <v>0.7648337872656629</v>
       </c>
       <c r="CA27" t="n">
         <v>0.7783768306470199</v>
@@ -10657,13 +10397,13 @@
         <v>0.8034525723281888</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.7667397304756253</v>
+        <v>0.7667397304756255</v>
       </c>
       <c r="CI27" t="n">
         <v>0.7725583571092197</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.7697765400331333</v>
+        <v>0.7697765400331336</v>
       </c>
       <c r="CK27" t="n">
         <v>0.7838412782180414</v>
@@ -10699,7 +10439,7 @@
         <v>0.7392144388676354</v>
       </c>
       <c r="CV27" t="n">
-        <v>0.7598226512591876</v>
+        <v>0.7598226512591874</v>
       </c>
       <c r="CW27" t="n">
         <v>0.8201010411844639</v>
@@ -10738,7 +10478,7 @@
         <v>0.6854646297292701</v>
       </c>
       <c r="DI27" t="n">
-        <v>0.7937538513140696</v>
+        <v>0.7937538513140695</v>
       </c>
       <c r="DJ27" t="n">
         <v>0.6868631035417405</v>
@@ -10771,7 +10511,7 @@
         <v>0.7433692120642529</v>
       </c>
       <c r="DT27" t="n">
-        <v>0.9444839455722041</v>
+        <v>0.9444839455722043</v>
       </c>
     </row>
     <row r="28">
@@ -10794,7 +10534,7 @@
         <v>0.7795970297651987</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7394597745855269</v>
+        <v>0.739459774585527</v>
       </c>
       <c r="H28" t="n">
         <v>0.7420556225025029</v>
@@ -10803,7 +10543,7 @@
         <v>0.6857309015103683</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7272862368601486</v>
+        <v>0.7272862368601484</v>
       </c>
       <c r="K28" t="n">
         <v>0.7778244563043025</v>
@@ -10857,7 +10597,7 @@
         <v>0.735705596262075</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.698307979374108</v>
+        <v>0.6983079793741082</v>
       </c>
       <c r="AC28" t="n">
         <v>0.7765346050078916</v>
@@ -10932,10 +10672,10 @@
         <v>0.7504054777915491</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.6956273325382482</v>
+        <v>0.6956273325382484</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.7397371604932799</v>
+        <v>0.7397371604932798</v>
       </c>
       <c r="BC28" t="n">
         <v>0.7239195748193077</v>
@@ -10953,7 +10693,7 @@
         <v>0.7449404519665279</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.7145358514968335</v>
+        <v>0.7145358514968334</v>
       </c>
       <c r="BI28" t="n">
         <v>1.06624334348407</v>
@@ -10980,7 +10720,7 @@
         <v>0.7266830360381086</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0.7455003348575454</v>
+        <v>0.7455003348575455</v>
       </c>
       <c r="BR28" t="n">
         <v>0.7120243726077456</v>
@@ -11022,7 +10762,7 @@
         <v>0.7576538120936319</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.7462672653405366</v>
+        <v>0.7462672653405367</v>
       </c>
       <c r="CF28" t="n">
         <v>0.7505128696985344</v>
@@ -11088,7 +10828,7 @@
         <v>0.7284573871922173</v>
       </c>
       <c r="DA28" t="n">
-        <v>0.7237536742160996</v>
+        <v>0.7237536742160998</v>
       </c>
       <c r="DB28" t="n">
         <v>0.6883154751336867</v>
@@ -11100,7 +10840,7 @@
         <v>0.7281067239766195</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.7052867874810391</v>
+        <v>0.7052867874810389</v>
       </c>
       <c r="DF28" t="n">
         <v>0.7132732353459238</v>
@@ -11127,7 +10867,7 @@
         <v>0.7661572987615833</v>
       </c>
       <c r="DN28" t="n">
-        <v>0.7145958148777111</v>
+        <v>0.714595814877711</v>
       </c>
       <c r="DO28" t="n">
         <v>0.7363748274094976</v>
@@ -11171,7 +10911,7 @@
         <v>0.711910975645881</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7231322960528955</v>
+        <v>0.7231322960528958</v>
       </c>
       <c r="I29" t="n">
         <v>0.6697012318774838</v>
@@ -11183,7 +10923,7 @@
         <v>0.7551964197443762</v>
       </c>
       <c r="L29" t="n">
-        <v>0.726131342780728</v>
+        <v>0.7261313427807281</v>
       </c>
       <c r="M29" t="n">
         <v>0.6758260031245312</v>
@@ -11228,7 +10968,7 @@
         <v>0.7144728777526496</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.7081839090604336</v>
+        <v>0.7081839090604335</v>
       </c>
       <c r="AB29" t="n">
         <v>0.6734927589415518</v>
@@ -11237,7 +10977,7 @@
         <v>0.7462556838477188</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.760727338266228</v>
+        <v>0.7607273382662278</v>
       </c>
       <c r="AE29" t="n">
         <v>0.758689694857822</v>
@@ -11249,7 +10989,7 @@
         <v>0.7391354862438808</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.7373126095289637</v>
+        <v>0.7373126095289639</v>
       </c>
       <c r="AI29" t="n">
         <v>0.7272016482479357</v>
@@ -11273,7 +11013,7 @@
         <v>0.6955521868220332</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.6845345433115301</v>
+        <v>0.6845345433115303</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.7386229331784258</v>
@@ -11288,10 +11028,10 @@
         <v>0.7256606328158838</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.7454890307927278</v>
+        <v>0.7454890307927277</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.6969552387567967</v>
+        <v>0.6969552387567965</v>
       </c>
       <c r="AW29" t="n">
         <v>0.7323917031800318</v>
@@ -11339,7 +11079,7 @@
         <v>0.7337678949168782</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.6832903445376926</v>
+        <v>0.6832903445376927</v>
       </c>
       <c r="BM29" t="n">
         <v>0.6921886385388774</v>
@@ -11351,7 +11091,7 @@
         <v>0.7319619509863381</v>
       </c>
       <c r="BP29" t="n">
-        <v>0.7014564750759711</v>
+        <v>0.7014564750759713</v>
       </c>
       <c r="BQ29" t="n">
         <v>0.7250309160011424</v>
@@ -11369,7 +11109,7 @@
         <v>0.7084972236402375</v>
       </c>
       <c r="BV29" t="n">
-        <v>0.6815249438642068</v>
+        <v>0.6815249438642067</v>
       </c>
       <c r="BW29" t="n">
         <v>0.7131519380357126</v>
@@ -11435,7 +11175,7 @@
         <v>0.7437445866146699</v>
       </c>
       <c r="CR29" t="n">
-        <v>0.7214969686589096</v>
+        <v>0.7214969686589094</v>
       </c>
       <c r="CS29" t="n">
         <v>0.6996293952619315</v>
@@ -11462,7 +11202,7 @@
         <v>0.7051123083214298</v>
       </c>
       <c r="DA29" t="n">
-        <v>0.7012046009807512</v>
+        <v>0.7012046009807514</v>
       </c>
       <c r="DB29" t="n">
         <v>0.6755876985561522</v>
@@ -11471,10 +11211,10 @@
         <v>0.6939489843120388</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.698954557694097</v>
+        <v>0.6989545576940971</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.6852766937176702</v>
+        <v>0.6852766937176704</v>
       </c>
       <c r="DF29" t="n">
         <v>0.6912024186177895</v>
@@ -11495,7 +11235,7 @@
         <v>0.7083768407549708</v>
       </c>
       <c r="DL29" t="n">
-        <v>0.722138629468984</v>
+        <v>0.7221386294689838</v>
       </c>
       <c r="DM29" t="n">
         <v>0.7367139315979749</v>
@@ -11533,7 +11273,7 @@
         <v>0.8980566753925711</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8955028881131241</v>
+        <v>0.8955028881131243</v>
       </c>
       <c r="E30" t="n">
         <v>0.8301541208998267</v>
@@ -11557,7 +11297,7 @@
         <v>0.7368160945782378</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7012005847070374</v>
+        <v>0.7012005847070372</v>
       </c>
       <c r="M30" t="n">
         <v>0.6625942008834194</v>
@@ -11611,7 +11351,7 @@
         <v>0.7205329945342083</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.7399268453784733</v>
+        <v>0.7399268453784731</v>
       </c>
       <c r="AE30" t="n">
         <v>0.7335203847790458</v>
@@ -11668,7 +11408,7 @@
         <v>0.6785744216908544</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.7102130189812326</v>
+        <v>0.7102130189812328</v>
       </c>
       <c r="AX30" t="n">
         <v>0.6689708786099977</v>
@@ -11713,13 +11453,13 @@
         <v>0.7125562569404679</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.6607480032718948</v>
+        <v>0.660748003271895</v>
       </c>
       <c r="BM30" t="n">
         <v>0.6711895618464373</v>
       </c>
       <c r="BN30" t="n">
-        <v>0.6892693891951219</v>
+        <v>0.6892693891951218</v>
       </c>
       <c r="BO30" t="n">
         <v>0.7079534744001801</v>
@@ -11734,13 +11474,13 @@
         <v>0.6791804097272238</v>
       </c>
       <c r="BS30" t="n">
-        <v>0.6615378784906585</v>
+        <v>0.6615378784906587</v>
       </c>
       <c r="BT30" t="n">
         <v>0.6950200923996322</v>
       </c>
       <c r="BU30" t="n">
-        <v>0.6852883002368991</v>
+        <v>0.6852883002368994</v>
       </c>
       <c r="BV30" t="n">
         <v>0.6661411437525772</v>
@@ -11755,7 +11495,7 @@
         <v>0.7071081166309422</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0.6887621062935299</v>
+        <v>0.68876210629353</v>
       </c>
       <c r="CA30" t="n">
         <v>0.6876262325478835</v>
@@ -11788,7 +11528,7 @@
         <v>0.7040098789563041</v>
       </c>
       <c r="CK30" t="n">
-        <v>0.7093170942561184</v>
+        <v>0.7093170942561182</v>
       </c>
       <c r="CL30" t="n">
         <v>0.6560052445002595</v>
@@ -11818,10 +11558,10 @@
         <v>0.6553884032797865</v>
       </c>
       <c r="CU30" t="n">
-        <v>0.669860051729147</v>
+        <v>0.6698600517291471</v>
       </c>
       <c r="CV30" t="n">
-        <v>0.7010693872632063</v>
+        <v>0.7010693872632062</v>
       </c>
       <c r="CW30" t="n">
         <v>0.7389069110854363</v>
@@ -11851,7 +11591,7 @@
         <v>0.670281508282579</v>
       </c>
       <c r="DF30" t="n">
-        <v>0.6755732739219535</v>
+        <v>0.6755732739219538</v>
       </c>
       <c r="DG30" t="n">
         <v>0.6985360901966149</v>
@@ -11881,7 +11621,7 @@
         <v>0.6922408319698133</v>
       </c>
       <c r="DP30" t="n">
-        <v>0.7259385515657548</v>
+        <v>0.725938551565755</v>
       </c>
       <c r="DQ30" t="n">
         <v>0.8409656176030024</v>
@@ -11893,7 +11633,7 @@
         <v>0.8054939294900271</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.947444123676059</v>
+        <v>0.9474441236760592</v>
       </c>
     </row>
     <row r="31">
@@ -11925,7 +11665,7 @@
         <v>0.6601457688545517</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6761345045193209</v>
+        <v>0.6761345045193208</v>
       </c>
       <c r="K31" t="n">
         <v>0.7217505215917402</v>
@@ -11946,13 +11686,13 @@
         <v>0.6516679289884961</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.7028150455601108</v>
+        <v>0.7028150455601107</v>
       </c>
       <c r="R31" t="n">
         <v>0.6767992453904583</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6704258074626956</v>
+        <v>0.6704258074626954</v>
       </c>
       <c r="T31" t="n">
         <v>0.6688621800533969</v>
@@ -12009,10 +11749,10 @@
         <v>0.6588679755294131</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.6625908539188834</v>
+        <v>0.6625908539188835</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.7000011204936638</v>
+        <v>0.7000011204936639</v>
       </c>
       <c r="AN31" t="n">
         <v>0.6809034514967589</v>
@@ -12054,13 +11794,13 @@
         <v>0.6881401627547991</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.6494708344411977</v>
+        <v>0.6494708344411976</v>
       </c>
       <c r="BB31" t="n">
         <v>0.6896492171300153</v>
       </c>
       <c r="BC31" t="n">
-        <v>0.6930040105496623</v>
+        <v>0.6930040105496621</v>
       </c>
       <c r="BD31" t="n">
         <v>0.6815013058113798</v>
@@ -12072,7 +11812,7 @@
         <v>0.7275068118406872</v>
       </c>
       <c r="BG31" t="n">
-        <v>0.6837394393065159</v>
+        <v>0.6837394393065158</v>
       </c>
       <c r="BH31" t="n">
         <v>0.6524460442416298</v>
@@ -12087,7 +11827,7 @@
         <v>0.6940037197407402</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.6444847480234442</v>
+        <v>0.6444847480234441</v>
       </c>
       <c r="BM31" t="n">
         <v>0.6546958771227687</v>
@@ -12099,7 +11839,7 @@
         <v>0.6871486395003255</v>
       </c>
       <c r="BP31" t="n">
-        <v>0.6664994160443302</v>
+        <v>0.6664994160443301</v>
       </c>
       <c r="BQ31" t="n">
         <v>0.6975645282582735</v>
@@ -12117,7 +11857,7 @@
         <v>0.6669003230911672</v>
       </c>
       <c r="BV31" t="n">
-        <v>0.6553276005740679</v>
+        <v>0.6553276005740678</v>
       </c>
       <c r="BW31" t="n">
         <v>0.6927909621444346</v>
@@ -12138,7 +11878,7 @@
         <v>0.6840779480841069</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.7063981002270331</v>
+        <v>0.706398100227033</v>
       </c>
       <c r="CD31" t="n">
         <v>0.6879946212493681</v>
@@ -12153,7 +11893,7 @@
         <v>0.7089211094087673</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.6785181316220409</v>
+        <v>0.678518131622041</v>
       </c>
       <c r="CI31" t="n">
         <v>0.6884236898687031</v>
@@ -12168,7 +11908,7 @@
         <v>0.6478632203468553</v>
       </c>
       <c r="CM31" t="n">
-        <v>0.698191699375087</v>
+        <v>0.6981916993750867</v>
       </c>
       <c r="CN31" t="n">
         <v>0.6664426718824986</v>
@@ -12198,10 +11938,10 @@
         <v>0.6905718892273854</v>
       </c>
       <c r="CW31" t="n">
-        <v>0.7200542203375182</v>
+        <v>0.7200542203375183</v>
       </c>
       <c r="CX31" t="n">
-        <v>0.6820302811652744</v>
+        <v>0.6820302811652746</v>
       </c>
       <c r="CY31" t="n">
         <v>0.6738379633443574</v>
@@ -12234,7 +11974,7 @@
         <v>0.6369815623644566</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.6866823750597844</v>
+        <v>0.6866823750597845</v>
       </c>
       <c r="DJ31" t="n">
         <v>0.6272160874159056</v>
@@ -12261,10 +12001,10 @@
         <v>0.8184392888369485</v>
       </c>
       <c r="DR31" t="n">
-        <v>0.8833545324271947</v>
+        <v>0.8833545324271949</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.8215797635227499</v>
+        <v>0.8215797635227498</v>
       </c>
       <c r="DT31" t="n">
         <v>0.9383032809660693</v>
@@ -12275,7 +12015,7 @@
         <v>0.8747475149456518</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7775935772502636</v>
+        <v>0.7775935772502637</v>
       </c>
       <c r="C32" t="n">
         <v>0.8863013508017682</v>
@@ -12299,7 +12039,7 @@
         <v>0.6634696731564503</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6712779156061377</v>
+        <v>0.6712779156061378</v>
       </c>
       <c r="K32" t="n">
         <v>0.709212828239111</v>
@@ -12332,13 +12072,13 @@
         <v>0.6610913981556787</v>
       </c>
       <c r="U32" t="n">
-        <v>0.6849264850052594</v>
+        <v>0.6849264850052597</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6417996977289763</v>
+        <v>0.6417996977289764</v>
       </c>
       <c r="W32" t="n">
-        <v>0.6549035674857563</v>
+        <v>0.6549035674857562</v>
       </c>
       <c r="X32" t="n">
         <v>0.6741813593130936</v>
@@ -12359,7 +12099,7 @@
         <v>0.6821385496584674</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.7070752264915841</v>
+        <v>0.7070752264915843</v>
       </c>
       <c r="AE32" t="n">
         <v>0.6937032143840682</v>
@@ -12386,13 +12126,13 @@
         <v>0.6540923204542073</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.6887863741230723</v>
+        <v>0.6887863741230722</v>
       </c>
       <c r="AN32" t="n">
         <v>0.6715011045770758</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.6635531495436585</v>
+        <v>0.6635531495436584</v>
       </c>
       <c r="AP32" t="n">
         <v>0.6416243392428057</v>
@@ -12404,7 +12144,7 @@
         <v>0.6989731009694299</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.6861119708608446</v>
+        <v>0.6861119708608449</v>
       </c>
       <c r="AT32" t="n">
         <v>0.6639753737494828</v>
@@ -12422,7 +12162,7 @@
         <v>0.6366198326417041</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.6546030335449046</v>
+        <v>0.6546030335449045</v>
       </c>
       <c r="AZ32" t="n">
         <v>0.6763035853055405</v>
@@ -12464,7 +12204,7 @@
         <v>0.6339899113997279</v>
       </c>
       <c r="BM32" t="n">
-        <v>0.6428025775471284</v>
+        <v>0.6428025775471286</v>
       </c>
       <c r="BN32" t="n">
         <v>0.6711624975453949</v>
@@ -12482,10 +12222,10 @@
         <v>0.6642429135468541</v>
       </c>
       <c r="BS32" t="n">
-        <v>0.6419433946509151</v>
+        <v>0.6419433946509152</v>
       </c>
       <c r="BT32" t="n">
-        <v>0.6592592152325872</v>
+        <v>0.6592592152325873</v>
       </c>
       <c r="BU32" t="n">
         <v>0.6534377137299683</v>
@@ -12500,7 +12240,7 @@
         <v>0.6681231322270625</v>
       </c>
       <c r="BY32" t="n">
-        <v>0.6791435487430406</v>
+        <v>0.6791435487430407</v>
       </c>
       <c r="BZ32" t="n">
         <v>0.6654392597943841</v>
@@ -12518,7 +12258,7 @@
         <v>0.6745006338312819</v>
       </c>
       <c r="CE32" t="n">
-        <v>0.6835826016916137</v>
+        <v>0.6835826016916138</v>
       </c>
       <c r="CF32" t="n">
         <v>0.6750752478302896</v>
@@ -12551,7 +12291,7 @@
         <v>0.6773365037901599</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.6724292456824208</v>
+        <v>0.6724292456824206</v>
       </c>
       <c r="CQ32" t="n">
         <v>0.6797371594170059</v>
@@ -12563,7 +12303,7 @@
         <v>0.6668942204864491</v>
       </c>
       <c r="CT32" t="n">
-        <v>0.6341872168265843</v>
+        <v>0.6341872168265844</v>
       </c>
       <c r="CU32" t="n">
         <v>0.6495538691614452</v>
@@ -12575,7 +12315,7 @@
         <v>0.7042862143184369</v>
       </c>
       <c r="CX32" t="n">
-        <v>0.6701481021217413</v>
+        <v>0.6701481021217414</v>
       </c>
       <c r="CY32" t="n">
         <v>0.6672491687503426</v>
@@ -12608,7 +12348,7 @@
         <v>0.6373355373839501</v>
       </c>
       <c r="DI32" t="n">
-        <v>0.6722766058040752</v>
+        <v>0.6722766058040751</v>
       </c>
       <c r="DJ32" t="n">
         <v>0.6249706572279169</v>
@@ -12685,7 +12425,7 @@
         <v>0.6517835771751653</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6708481143619708</v>
+        <v>0.6708481143619709</v>
       </c>
       <c r="O33" t="n">
         <v>0.6835159003956449</v>
@@ -12718,7 +12458,7 @@
         <v>0.6660587220782043</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.6416292943563968</v>
+        <v>0.6416292943563969</v>
       </c>
       <c r="Z33" t="n">
         <v>0.6675610985056082</v>
@@ -12727,7 +12467,7 @@
         <v>0.6526527549248262</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.6385040839918656</v>
+        <v>0.6385040839918658</v>
       </c>
       <c r="AC33" t="n">
         <v>0.6690306288001612</v>
@@ -12757,7 +12497,7 @@
         <v>0.6433844097057015</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.6498881752432721</v>
+        <v>0.649888175243272</v>
       </c>
       <c r="AM33" t="n">
         <v>0.6800910366657568</v>
@@ -12769,13 +12509,13 @@
         <v>0.6609692348594193</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.6358693411000659</v>
+        <v>0.635869341100066</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.6848169558340657</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.6858345448841715</v>
+        <v>0.6858345448841716</v>
       </c>
       <c r="AS33" t="n">
         <v>0.6728378322803168</v>
@@ -12814,7 +12554,7 @@
         <v>0.6449598396932205</v>
       </c>
       <c r="BE33" t="n">
-        <v>0.6397894347569735</v>
+        <v>0.6397894347569734</v>
       </c>
       <c r="BF33" t="n">
         <v>0.7029849109683619</v>
@@ -12874,7 +12614,7 @@
         <v>0.6651730552706094</v>
       </c>
       <c r="BY33" t="n">
-        <v>0.6711706698745771</v>
+        <v>0.671170669874577</v>
       </c>
       <c r="BZ33" t="n">
         <v>0.6596384179815235</v>
@@ -12889,10 +12629,10 @@
         <v>0.6941098703510598</v>
       </c>
       <c r="CD33" t="n">
-        <v>0.6652760951960087</v>
+        <v>0.6652760951960088</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.6780671802569954</v>
+        <v>0.6780671802569953</v>
       </c>
       <c r="CF33" t="n">
         <v>0.6664802858807813</v>
@@ -12904,10 +12644,10 @@
         <v>0.6568676389581695</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.6693989156559496</v>
+        <v>0.6693989156559497</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.6767959563424181</v>
+        <v>0.6767959563424182</v>
       </c>
       <c r="CK33" t="n">
         <v>0.6721048266196772</v>
@@ -12952,7 +12692,7 @@
         <v>0.6616294325441281</v>
       </c>
       <c r="CY33" t="n">
-        <v>0.6635232484665914</v>
+        <v>0.6635232484665915</v>
       </c>
       <c r="CZ33" t="n">
         <v>0.6644477097754146</v>
@@ -12988,10 +12728,10 @@
         <v>0.6267341220086728</v>
       </c>
       <c r="DK33" t="n">
-        <v>0.6676633893575149</v>
+        <v>0.6676633893575147</v>
       </c>
       <c r="DL33" t="n">
-        <v>0.6572119124652928</v>
+        <v>0.6572119124652925</v>
       </c>
       <c r="DM33" t="n">
         <v>0.6629505203634939</v>
@@ -13038,7 +12778,7 @@
         <v>0.7156675372120033</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6859188868495473</v>
+        <v>0.685918886849547</v>
       </c>
       <c r="H34" t="n">
         <v>0.6777475489608341</v>
@@ -13050,7 +12790,7 @@
         <v>0.6740813684350589</v>
       </c>
       <c r="K34" t="n">
-        <v>0.690756819274994</v>
+        <v>0.6907568192749941</v>
       </c>
       <c r="L34" t="n">
         <v>0.6437088327627354</v>
@@ -13065,7 +12805,7 @@
         <v>0.6831498658213477</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6424111199787009</v>
+        <v>0.642411119978701</v>
       </c>
       <c r="Q34" t="n">
         <v>0.6924603279062086</v>
@@ -13134,7 +12874,7 @@
         <v>0.649516943735627</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.673982944675602</v>
+        <v>0.6739829446756019</v>
       </c>
       <c r="AN34" t="n">
         <v>0.6626795728880025</v>
@@ -13158,13 +12898,13 @@
         <v>0.642146544301551</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.6746381463573129</v>
+        <v>0.6746381463573128</v>
       </c>
       <c r="AV34" t="n">
         <v>0.6413140676662871</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.6581440649956751</v>
+        <v>0.6581440649956749</v>
       </c>
       <c r="AX34" t="n">
         <v>0.6223010696832819</v>
@@ -13182,7 +12922,7 @@
         <v>0.6647429184306203</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.6841271909376775</v>
+        <v>0.6841271909376774</v>
       </c>
       <c r="BD34" t="n">
         <v>0.6304236115973075</v>
@@ -13209,7 +12949,7 @@
         <v>0.6539320392898713</v>
       </c>
       <c r="BL34" t="n">
-        <v>0.6288035854791882</v>
+        <v>0.6288035854791881</v>
       </c>
       <c r="BM34" t="n">
         <v>0.6335851693202057</v>
@@ -13227,7 +12967,7 @@
         <v>0.6831971808746881</v>
       </c>
       <c r="BR34" t="n">
-        <v>0.6628214847954397</v>
+        <v>0.6628214847954396</v>
       </c>
       <c r="BS34" t="n">
         <v>0.6432429116581359</v>
@@ -13314,7 +13054,7 @@
         <v>0.6320298631665693</v>
       </c>
       <c r="CU34" t="n">
-        <v>0.6473455331048129</v>
+        <v>0.6473455331048128</v>
       </c>
       <c r="CV34" t="n">
         <v>0.6756483225167897</v>
@@ -13341,7 +13081,7 @@
         <v>0.6420922382861401</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.638946220666467</v>
+        <v>0.6389462206664671</v>
       </c>
       <c r="DE34" t="n">
         <v>0.6553945902764109</v>
@@ -13350,10 +13090,10 @@
         <v>0.6606439902705521</v>
       </c>
       <c r="DG34" t="n">
-        <v>0.6636294583156008</v>
+        <v>0.6636294583156007</v>
       </c>
       <c r="DH34" t="n">
-        <v>0.6500977602730392</v>
+        <v>0.6500977602730391</v>
       </c>
       <c r="DI34" t="n">
         <v>0.6564206919546897</v>
@@ -13365,7 +13105,7 @@
         <v>0.6651227913366281</v>
       </c>
       <c r="DL34" t="n">
-        <v>0.6519737524968841</v>
+        <v>0.6519737524968842</v>
       </c>
       <c r="DM34" t="n">
         <v>0.6580721501804878</v>
@@ -13377,7 +13117,7 @@
         <v>0.656592920699177</v>
       </c>
       <c r="DP34" t="n">
-        <v>0.6783097522537389</v>
+        <v>0.6783097522537388</v>
       </c>
       <c r="DQ34" t="n">
         <v>0.7646929311827677</v>
@@ -13463,10 +13203,10 @@
         <v>0.6702322048945443</v>
       </c>
       <c r="X35" t="n">
-        <v>0.6613165287245487</v>
+        <v>0.6613165287245488</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.6383083103070435</v>
+        <v>0.6383083103070436</v>
       </c>
       <c r="Z35" t="n">
         <v>0.6662047543199716</v>
@@ -13481,7 +13221,7 @@
         <v>0.6538796189926529</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.6734380896968939</v>
+        <v>0.673438089696894</v>
       </c>
       <c r="AE35" t="n">
         <v>0.6622993120827103</v>
@@ -13496,7 +13236,7 @@
         <v>0.6544720868492259</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.6386207397462539</v>
+        <v>0.638620739746254</v>
       </c>
       <c r="AJ35" t="n">
         <v>0.6536294000373074</v>
@@ -13508,7 +13248,7 @@
         <v>0.6525033140304867</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.6704590114071353</v>
+        <v>0.6704590114071354</v>
       </c>
       <c r="AN35" t="n">
         <v>0.6634873486531719</v>
@@ -13538,7 +13278,7 @@
         <v>0.6413890158472081</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.6543768012881418</v>
+        <v>0.6543768012881419</v>
       </c>
       <c r="AX35" t="n">
         <v>0.6217080845449178</v>
@@ -13547,7 +13287,7 @@
         <v>0.6455028908661206</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.6620916541604104</v>
+        <v>0.6620916541604105</v>
       </c>
       <c r="BA35" t="n">
         <v>0.6445027609160044</v>
@@ -13619,13 +13359,13 @@
         <v>0.6963959878088209</v>
       </c>
       <c r="BX35" t="n">
-        <v>0.6697656595278552</v>
+        <v>0.6697656595278553</v>
       </c>
       <c r="BY35" t="n">
         <v>0.6636575135691433</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0.6586533698458057</v>
+        <v>0.6586533698458058</v>
       </c>
       <c r="CA35" t="n">
         <v>0.6393988923508017</v>
@@ -13643,7 +13383,7 @@
         <v>0.6759352550948676</v>
       </c>
       <c r="CF35" t="n">
-        <v>0.6599204804810332</v>
+        <v>0.6599204804810334</v>
       </c>
       <c r="CG35" t="n">
         <v>0.663362352511868</v>
@@ -13673,7 +13413,7 @@
         <v>0.6693654428794167</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.6708128473050787</v>
+        <v>0.6708128473050786</v>
       </c>
       <c r="CQ35" t="n">
         <v>0.6533640968665162</v>
@@ -13694,7 +13434,7 @@
         <v>0.674496188827998</v>
       </c>
       <c r="CW35" t="n">
-        <v>0.6734944363454123</v>
+        <v>0.6734944363454122</v>
       </c>
       <c r="CX35" t="n">
         <v>0.653949601994855</v>
@@ -13703,7 +13443,7 @@
         <v>0.663861218747047</v>
       </c>
       <c r="CZ35" t="n">
-        <v>0.6681453289213434</v>
+        <v>0.6681453289213435</v>
       </c>
       <c r="DA35" t="n">
         <v>0.64429028677738</v>
@@ -13739,7 +13479,7 @@
         <v>0.6658594716635806</v>
       </c>
       <c r="DL35" t="n">
-        <v>0.6500455077539524</v>
+        <v>0.6500455077539525</v>
       </c>
       <c r="DM35" t="n">
         <v>0.6592532372196631</v>
@@ -13828,7 +13568,7 @@
         <v>0.6660137698291605</v>
       </c>
       <c r="U36" t="n">
-        <v>0.7076027176487415</v>
+        <v>0.7076027176487416</v>
       </c>
       <c r="V36" t="n">
         <v>0.6679462557717891</v>
@@ -13837,13 +13577,13 @@
         <v>0.68053092480946</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6639125319085272</v>
+        <v>0.6639125319085273</v>
       </c>
       <c r="Y36" t="n">
         <v>0.6420883250303531</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.6705158840408469</v>
+        <v>0.6705158840408471</v>
       </c>
       <c r="AA36" t="n">
         <v>0.6520021899982718</v>
@@ -13855,13 +13595,13 @@
         <v>0.6514661945495948</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.6673306421857177</v>
+        <v>0.6673306421857175</v>
       </c>
       <c r="AE36" t="n">
         <v>0.6598273913424826</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.6745386663547374</v>
+        <v>0.6745386663547375</v>
       </c>
       <c r="AG36" t="n">
         <v>0.6416835908301735</v>
@@ -13870,7 +13610,7 @@
         <v>0.6516055923430267</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.638363734213057</v>
+        <v>0.6383637342130569</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.6514772298780549</v>
@@ -13882,7 +13622,7 @@
         <v>0.6584012083697619</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.6695335926074039</v>
+        <v>0.6695335926074041</v>
       </c>
       <c r="AN36" t="n">
         <v>0.6674034652053117</v>
@@ -13900,10 +13640,10 @@
         <v>0.6660571518183747</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.6536817805140046</v>
+        <v>0.6536817805140047</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.6356516851072816</v>
+        <v>0.6356516851072818</v>
       </c>
       <c r="AU36" t="n">
         <v>0.6743965158260042</v>
@@ -13942,7 +13682,7 @@
         <v>0.6896778482446793</v>
       </c>
       <c r="BG36" t="n">
-        <v>0.6654161414806974</v>
+        <v>0.6654161414806973</v>
       </c>
       <c r="BH36" t="n">
         <v>0.6344749830031642</v>
@@ -14020,7 +13760,7 @@
         <v>0.6616632653444346</v>
       </c>
       <c r="CG36" t="n">
-        <v>0.6592882007331039</v>
+        <v>0.6592882007331037</v>
       </c>
       <c r="CH36" t="n">
         <v>0.6535247979411054</v>
@@ -14053,7 +13793,7 @@
         <v>0.6520742636244664</v>
       </c>
       <c r="CR36" t="n">
-        <v>0.6761456750021984</v>
+        <v>0.6761456750021986</v>
       </c>
       <c r="CS36" t="n">
         <v>0.67210689864188</v>
@@ -14086,7 +13826,7 @@
         <v>0.6805360501064626</v>
       </c>
       <c r="DC36" t="n">
-        <v>0.6613775364668474</v>
+        <v>0.6613775364668472</v>
       </c>
       <c r="DD36" t="n">
         <v>0.6519761046739464</v>
@@ -14160,10 +13900,10 @@
         <v>0.7339679778636058</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7149916915932052</v>
+        <v>0.7149916915932053</v>
       </c>
       <c r="H37" t="n">
-        <v>0.681804757594124</v>
+        <v>0.6818047575941241</v>
       </c>
       <c r="I37" t="n">
         <v>0.7098641885228258</v>
@@ -14181,7 +13921,7 @@
         <v>0.6888967100775277</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6719422447285452</v>
+        <v>0.6719422447285451</v>
       </c>
       <c r="O37" t="n">
         <v>0.699756639816793</v>
@@ -14217,13 +13957,13 @@
         <v>0.649388849040629</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.6779691457301682</v>
+        <v>0.6779691457301683</v>
       </c>
       <c r="AA37" t="n">
         <v>0.6566788055057029</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.67393403408564</v>
+        <v>0.6739340340856401</v>
       </c>
       <c r="AC37" t="n">
         <v>0.6524388969679336</v>
@@ -14268,7 +14008,7 @@
         <v>0.6499389612335164</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.6817227309014482</v>
+        <v>0.6817227309014484</v>
       </c>
       <c r="AR37" t="n">
         <v>0.6653062744723443</v>
@@ -14298,7 +14038,7 @@
         <v>0.6686189267313525</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.6609958725484805</v>
+        <v>0.6609958725484804</v>
       </c>
       <c r="BB37" t="n">
         <v>0.6573711879699705</v>
@@ -14376,10 +14116,10 @@
         <v>0.6696789792060354</v>
       </c>
       <c r="CA37" t="n">
-        <v>0.6468981402480314</v>
+        <v>0.6468981402480313</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.6741308190104039</v>
+        <v>0.6741308190104038</v>
       </c>
       <c r="CC37" t="n">
         <v>0.7067497699310376</v>
@@ -14400,7 +14140,7 @@
         <v>0.6597879167165439</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.6717248235161115</v>
+        <v>0.6717248235161114</v>
       </c>
       <c r="CJ37" t="n">
         <v>0.6807172643535246</v>
@@ -14424,7 +14164,7 @@
         <v>0.6823308195980944</v>
       </c>
       <c r="CQ37" t="n">
-        <v>0.6536088460936568</v>
+        <v>0.6536088460936569</v>
       </c>
       <c r="CR37" t="n">
         <v>0.6802628528842279</v>
@@ -14469,7 +14209,7 @@
         <v>0.6807819057249688</v>
       </c>
       <c r="DF37" t="n">
-        <v>0.6831778674622258</v>
+        <v>0.6831778674622259</v>
       </c>
       <c r="DG37" t="n">
         <v>0.6629048835485896</v>
@@ -14505,7 +14245,7 @@
         <v>0.7393199076950353</v>
       </c>
       <c r="DR37" t="n">
-        <v>0.8362813547461688</v>
+        <v>0.8362813547461687</v>
       </c>
       <c r="DS37" t="n">
         <v>0.8824667113215645</v>
@@ -14519,7 +14259,7 @@
         <v>0.8587507407007139</v>
       </c>
       <c r="B38" t="n">
-        <v>0.862004842985918</v>
+        <v>0.8620048429859181</v>
       </c>
       <c r="C38" t="n">
         <v>0.8189835877145999</v>
@@ -14534,13 +14274,13 @@
         <v>0.7429522082846136</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7273665325064007</v>
+        <v>0.7273665325064006</v>
       </c>
       <c r="H38" t="n">
         <v>0.6902184808088033</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7215567891816522</v>
+        <v>0.7215567891816521</v>
       </c>
       <c r="J38" t="n">
         <v>0.7103581561036501</v>
@@ -14570,7 +14310,7 @@
         <v>0.7002511022220952</v>
       </c>
       <c r="S38" t="n">
-        <v>0.6633549856530159</v>
+        <v>0.663354985653016</v>
       </c>
       <c r="T38" t="n">
         <v>0.6833467089698462</v>
@@ -14582,7 +14322,7 @@
         <v>0.6978914839151888</v>
       </c>
       <c r="W38" t="n">
-        <v>0.7055708014529839</v>
+        <v>0.7055708014529838</v>
       </c>
       <c r="X38" t="n">
         <v>0.6768503958556611</v>
@@ -14594,7 +14334,7 @@
         <v>0.6882924091986047</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.6632417428866748</v>
+        <v>0.6632417428866749</v>
       </c>
       <c r="AB38" t="n">
         <v>0.6883919396022579</v>
@@ -14606,7 +14346,7 @@
         <v>0.6661047904406109</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.6655757120959621</v>
+        <v>0.6655757120959622</v>
       </c>
       <c r="AF38" t="n">
         <v>0.6867299580489321</v>
@@ -14636,7 +14376,7 @@
         <v>0.6827315051264568</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.6944586207361736</v>
+        <v>0.6944586207361737</v>
       </c>
       <c r="AP38" t="n">
         <v>0.6629058645055591</v>
@@ -14648,13 +14388,13 @@
         <v>0.6671223028577291</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.658159069074436</v>
+        <v>0.6581590690744358</v>
       </c>
       <c r="AT38" t="n">
         <v>0.6471635522018283</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.6858316077102198</v>
+        <v>0.6858316077102199</v>
       </c>
       <c r="AV38" t="n">
         <v>0.6653776356860649</v>
@@ -14687,7 +14427,7 @@
         <v>0.6623583456190981</v>
       </c>
       <c r="BF38" t="n">
-        <v>0.6935632256324836</v>
+        <v>0.6935632256324835</v>
       </c>
       <c r="BG38" t="n">
         <v>0.6763658881443929</v>
@@ -14699,7 +14439,7 @@
         <v>0.7547121492506117</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.6685380829340074</v>
+        <v>0.6685380829340073</v>
       </c>
       <c r="BK38" t="n">
         <v>0.6480135151172293</v>
@@ -14735,13 +14475,13 @@
         <v>0.6648396523323852</v>
       </c>
       <c r="BV38" t="n">
-        <v>0.6916140852524227</v>
+        <v>0.6916140852524225</v>
       </c>
       <c r="BW38" t="n">
         <v>0.7168941103336086</v>
       </c>
       <c r="BX38" t="n">
-        <v>0.6922366966531733</v>
+        <v>0.6922366966531734</v>
       </c>
       <c r="BY38" t="n">
         <v>0.6726576161106426</v>
@@ -14771,7 +14511,7 @@
         <v>0.6638887735923589</v>
       </c>
       <c r="CH38" t="n">
-        <v>0.6694438720729055</v>
+        <v>0.6694438720729052</v>
       </c>
       <c r="CI38" t="n">
         <v>0.6796231287737531</v>
@@ -14789,7 +14529,7 @@
         <v>0.6892356098113488</v>
       </c>
       <c r="CN38" t="n">
-        <v>0.667353445559851</v>
+        <v>0.6673534455598509</v>
       </c>
       <c r="CO38" t="n">
         <v>0.6804972841845357</v>
@@ -14896,7 +14636,7 @@
         <v>0.8736606825960348</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8118415867742003</v>
+        <v>0.8118415867742002</v>
       </c>
       <c r="D39" t="n">
         <v>0.8087903111157735</v>
@@ -14929,10 +14669,10 @@
         <v>0.7178401614274776</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6877424555795937</v>
+        <v>0.6877424555795938</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7209434665827189</v>
+        <v>0.720943466582719</v>
       </c>
       <c r="P39" t="n">
         <v>0.7053506842132223</v>
@@ -14941,7 +14681,7 @@
         <v>0.7286439120078669</v>
       </c>
       <c r="R39" t="n">
-        <v>0.7140916246985654</v>
+        <v>0.7140916246985652</v>
       </c>
       <c r="S39" t="n">
         <v>0.675873368241977</v>
@@ -14956,7 +14696,7 @@
         <v>0.7154721510958409</v>
       </c>
       <c r="W39" t="n">
-        <v>0.7195987165955048</v>
+        <v>0.7195987165955049</v>
       </c>
       <c r="X39" t="n">
         <v>0.6870090558324897</v>
@@ -14968,7 +14708,7 @@
         <v>0.7011467352827058</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.6717916040814652</v>
+        <v>0.6717916040814653</v>
       </c>
       <c r="AB39" t="n">
         <v>0.7050644675886644</v>
@@ -15019,7 +14759,7 @@
         <v>0.6959889509774033</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.6716588404396419</v>
+        <v>0.6716588404396416</v>
       </c>
       <c r="AS39" t="n">
         <v>0.6647355456515173</v>
@@ -15037,7 +14777,7 @@
         <v>0.6772385237647378</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.6631431670669977</v>
+        <v>0.6631431670669976</v>
       </c>
       <c r="AY39" t="n">
         <v>0.684659238216453</v>
@@ -15082,7 +14822,7 @@
         <v>0.6797883220180194</v>
       </c>
       <c r="BM39" t="n">
-        <v>0.6789715113594128</v>
+        <v>0.678971511359413</v>
       </c>
       <c r="BN39" t="n">
         <v>0.7024644441124008</v>
@@ -15103,13 +14843,13 @@
         <v>0.7034362009340576</v>
       </c>
       <c r="BT39" t="n">
-        <v>0.6820763546319037</v>
+        <v>0.6820763546319036</v>
       </c>
       <c r="BU39" t="n">
         <v>0.6772906730153059</v>
       </c>
       <c r="BV39" t="n">
-        <v>0.707645106083815</v>
+        <v>0.7076451060838149</v>
       </c>
       <c r="BW39" t="n">
         <v>0.7241875060455043</v>
@@ -15169,10 +14909,10 @@
         <v>0.6890470677336663</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.7029904081478365</v>
+        <v>0.7029904081478364</v>
       </c>
       <c r="CQ39" t="n">
-        <v>0.6636771533113344</v>
+        <v>0.6636771533113341</v>
       </c>
       <c r="CR39" t="n">
         <v>0.6941041450388689</v>
@@ -15196,7 +14936,7 @@
         <v>0.6700707541246641</v>
       </c>
       <c r="CY39" t="n">
-        <v>0.6988657741142409</v>
+        <v>0.6988657741142407</v>
       </c>
       <c r="CZ39" t="n">
         <v>0.6962006279013583</v>
@@ -15208,7 +14948,7 @@
         <v>0.709569332129723</v>
       </c>
       <c r="DC39" t="n">
-        <v>0.7020330024164146</v>
+        <v>0.7020330024164148</v>
       </c>
       <c r="DD39" t="n">
         <v>0.692997657181207</v>
@@ -15244,13 +14984,13 @@
         <v>0.6794113388154793</v>
       </c>
       <c r="DO39" t="n">
-        <v>0.6839538676544902</v>
+        <v>0.6839538676544903</v>
       </c>
       <c r="DP39" t="n">
         <v>0.7020625100865053</v>
       </c>
       <c r="DQ39" t="n">
-        <v>0.7357071739290887</v>
+        <v>0.7357071739290888</v>
       </c>
       <c r="DR39" t="n">
         <v>0.8439214499244136</v>
@@ -15315,19 +15055,19 @@
         <v>0.7423355253288342</v>
       </c>
       <c r="R40" t="n">
-        <v>0.7298205352815694</v>
+        <v>0.7298205352815696</v>
       </c>
       <c r="S40" t="n">
         <v>0.6921755295602985</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7127444831101128</v>
+        <v>0.7127444831101127</v>
       </c>
       <c r="U40" t="n">
-        <v>0.7343262029121146</v>
+        <v>0.7343262029121147</v>
       </c>
       <c r="V40" t="n">
-        <v>0.7348768815289349</v>
+        <v>0.7348768815289352</v>
       </c>
       <c r="W40" t="n">
         <v>0.7348189860208626</v>
@@ -15348,7 +15088,7 @@
         <v>0.7247390814625343</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.6784431249261169</v>
+        <v>0.678443124926117</v>
       </c>
       <c r="AD40" t="n">
         <v>0.6811156065837861</v>
@@ -15393,13 +15133,13 @@
         <v>0.7069278265057384</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.6794043813279134</v>
+        <v>0.6794043813279131</v>
       </c>
       <c r="AS40" t="n">
         <v>0.6741234440057235</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.6778503374578626</v>
+        <v>0.6778503374578627</v>
       </c>
       <c r="AU40" t="n">
         <v>0.7046312459145879</v>
@@ -15471,7 +15211,7 @@
         <v>0.7140711707424687</v>
       </c>
       <c r="BR40" t="n">
-        <v>0.7135803135957298</v>
+        <v>0.71358031359573</v>
       </c>
       <c r="BS40" t="n">
         <v>0.7196547562032789</v>
@@ -15507,10 +15247,10 @@
         <v>0.7379646432688869</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.6912228131069583</v>
+        <v>0.6912228131069582</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.710693281446603</v>
+        <v>0.7106932814466033</v>
       </c>
       <c r="CF40" t="n">
         <v>0.6969984997523285</v>
@@ -15582,7 +15322,7 @@
         <v>0.7252604749658158</v>
       </c>
       <c r="DC40" t="n">
-        <v>0.7165911033813359</v>
+        <v>0.7165911033813358</v>
       </c>
       <c r="DD40" t="n">
         <v>0.7092043520036059</v>
@@ -15597,13 +15337,13 @@
         <v>0.6854423837117443</v>
       </c>
       <c r="DH40" t="n">
-        <v>0.752652272247206</v>
+        <v>0.7526522722472062</v>
       </c>
       <c r="DI40" t="n">
         <v>0.6878620973462803</v>
       </c>
       <c r="DJ40" t="n">
-        <v>0.7139684254472095</v>
+        <v>0.7139684254472097</v>
       </c>
       <c r="DK40" t="n">
         <v>0.7160112283804126</v>
@@ -15630,7 +15370,7 @@
         <v>0.8525823448093192</v>
       </c>
       <c r="DS40" t="n">
-        <v>0.9024588079629566</v>
+        <v>0.9024588079629564</v>
       </c>
       <c r="DT40" t="n">
         <v>0.8220948930310263</v>
@@ -15767,7 +15507,7 @@
         <v>0.7207001079752773</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.6910552538799659</v>
+        <v>0.6910552538799658</v>
       </c>
       <c r="AS41" t="n">
         <v>0.6867016627940442</v>
@@ -15788,7 +15528,7 @@
         <v>0.7064999593012481</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.7266206793861201</v>
+        <v>0.7266206793861203</v>
       </c>
       <c r="AZ41" t="n">
         <v>0.71111588484097</v>
@@ -15821,7 +15561,7 @@
         <v>0.6967882131613456</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0.7122248139465559</v>
+        <v>0.7122248139465558</v>
       </c>
       <c r="BK41" t="n">
         <v>0.6796912813846109</v>
@@ -15839,7 +15579,7 @@
         <v>0.6942164646957474</v>
       </c>
       <c r="BP41" t="n">
-        <v>0.7181633342937163</v>
+        <v>0.7181633342937164</v>
       </c>
       <c r="BQ41" t="n">
         <v>0.7238892650386798</v>
@@ -15911,7 +15651,7 @@
         <v>0.7272458880675955</v>
       </c>
       <c r="CN41" t="n">
-        <v>0.7178097984000338</v>
+        <v>0.7178097984000339</v>
       </c>
       <c r="CO41" t="n">
         <v>0.7159823406055901</v>
@@ -15935,7 +15675,7 @@
         <v>0.7302365008355425</v>
       </c>
       <c r="CV41" t="n">
-        <v>0.7003393681328705</v>
+        <v>0.7003393681328707</v>
       </c>
       <c r="CW41" t="n">
         <v>0.7052688724010375</v>
@@ -15950,7 +15690,7 @@
         <v>0.7169265107464182</v>
       </c>
       <c r="DA41" t="n">
-        <v>0.715208499178167</v>
+        <v>0.7152084991781672</v>
       </c>
       <c r="DB41" t="n">
         <v>0.7451307247569507</v>
@@ -16004,7 +15744,7 @@
         <v>0.8635828578959229</v>
       </c>
       <c r="DS41" t="n">
-        <v>0.9078787970579234</v>
+        <v>0.9078787970579235</v>
       </c>
       <c r="DT41" t="n">
         <v>0.818491747652941</v>
@@ -16012,19 +15752,19 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8277060917404163</v>
+        <v>0.8277060917404162</v>
       </c>
       <c r="B42" t="n">
-        <v>0.893260951027646</v>
+        <v>0.8932609510276462</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8069163658827833</v>
+        <v>0.8069163658827835</v>
       </c>
       <c r="D42" t="n">
         <v>0.809743162818951</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7919918841081759</v>
+        <v>0.791991884108176</v>
       </c>
       <c r="F42" t="n">
         <v>0.7907622306367548</v>
@@ -16036,7 +15776,7 @@
         <v>0.77317011993007</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8005207553556112</v>
+        <v>0.8005207553556113</v>
       </c>
       <c r="J42" t="n">
         <v>0.7589076848625828</v>
@@ -16060,7 +15800,7 @@
         <v>0.7979715208874056</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.7734544242529467</v>
+        <v>0.7734544242529466</v>
       </c>
       <c r="R42" t="n">
         <v>0.7679814829388641</v>
@@ -16120,7 +15860,7 @@
         <v>0.6994525775680143</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.754450232003766</v>
+        <v>0.7544502320037659</v>
       </c>
       <c r="AL42" t="n">
         <v>0.7540119128288264</v>
@@ -16129,10 +15869,10 @@
         <v>0.7343893091937801</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.7457206548784437</v>
+        <v>0.7457206548784439</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.7615775305161924</v>
+        <v>0.7615775305161921</v>
       </c>
       <c r="AP42" t="n">
         <v>0.7581061475999451</v>
@@ -16204,22 +15944,22 @@
         <v>0.7290911002124688</v>
       </c>
       <c r="BM42" t="n">
-        <v>0.7387630673149556</v>
+        <v>0.7387630673149557</v>
       </c>
       <c r="BN42" t="n">
-        <v>0.7519616122214705</v>
+        <v>0.7519616122214703</v>
       </c>
       <c r="BO42" t="n">
         <v>0.7147264176095925</v>
       </c>
       <c r="BP42" t="n">
-        <v>0.7417679991592611</v>
+        <v>0.7417679991592612</v>
       </c>
       <c r="BQ42" t="n">
         <v>0.7355270768876692</v>
       </c>
       <c r="BR42" t="n">
-        <v>0.7457504973969404</v>
+        <v>0.7457504973969405</v>
       </c>
       <c r="BS42" t="n">
         <v>0.7577852079967139</v>
@@ -16231,7 +15971,7 @@
         <v>0.7329479162167414</v>
       </c>
       <c r="BV42" t="n">
-        <v>0.7641416679531738</v>
+        <v>0.764141667953174</v>
       </c>
       <c r="BW42" t="n">
         <v>0.7516775275931817</v>
@@ -16255,7 +15995,7 @@
         <v>0.7649419625713356</v>
       </c>
       <c r="CD42" t="n">
-        <v>0.7311965150837382</v>
+        <v>0.7311965150837384</v>
       </c>
       <c r="CE42" t="n">
         <v>0.7457406239694097</v>
@@ -16279,13 +16019,13 @@
         <v>0.7411739806474508</v>
       </c>
       <c r="CL42" t="n">
-        <v>0.7925098466725958</v>
+        <v>0.7925098466725961</v>
       </c>
       <c r="CM42" t="n">
         <v>0.7429923989668419</v>
       </c>
       <c r="CN42" t="n">
-        <v>0.7402998327666185</v>
+        <v>0.7402998327666184</v>
       </c>
       <c r="CO42" t="n">
         <v>0.735374770537585</v>
@@ -16297,7 +16037,7 @@
         <v>0.7002852064596159</v>
       </c>
       <c r="CR42" t="n">
-        <v>0.7409922692904548</v>
+        <v>0.740992269290455</v>
       </c>
       <c r="CS42" t="n">
         <v>0.7713023335532379</v>
@@ -16309,7 +16049,7 @@
         <v>0.7532101402415734</v>
       </c>
       <c r="CV42" t="n">
-        <v>0.7135501714736407</v>
+        <v>0.7135501714736409</v>
       </c>
       <c r="CW42" t="n">
         <v>0.7227240962804728</v>
@@ -16369,7 +16109,7 @@
         <v>0.7369238464460141</v>
       </c>
       <c r="DP42" t="n">
-        <v>0.7373315952800451</v>
+        <v>0.7373315952800453</v>
       </c>
       <c r="DQ42" t="n">
         <v>0.7462591573816908</v>
@@ -16381,7 +16121,7 @@
         <v>0.9120533387743756</v>
       </c>
       <c r="DT42" t="n">
-        <v>0.8170621594030271</v>
+        <v>0.817062159403027</v>
       </c>
     </row>
     <row r="43">
@@ -16479,7 +16219,7 @@
         <v>0.733129867518541</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.7706803896463283</v>
+        <v>0.7706803896463282</v>
       </c>
       <c r="AG43" t="n">
         <v>0.747777454690559</v>
@@ -16509,7 +16249,7 @@
         <v>0.7851276393386903</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.7916679129720201</v>
+        <v>0.7916679129720203</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.757508421439558</v>
@@ -16521,7 +16261,7 @@
         <v>0.7236332611131874</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.7552073714578457</v>
+        <v>0.7552073714578459</v>
       </c>
       <c r="AU43" t="n">
         <v>0.7473561543986906</v>
@@ -16569,7 +16309,7 @@
         <v>0.667286501373334</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.7553567820392878</v>
+        <v>0.7553567820392877</v>
       </c>
       <c r="BK43" t="n">
         <v>0.7199363004864802</v>
@@ -16659,7 +16399,7 @@
         <v>0.7608662407905171</v>
       </c>
       <c r="CN43" t="n">
-        <v>0.7663068197290969</v>
+        <v>0.7663068197290966</v>
       </c>
       <c r="CO43" t="n">
         <v>0.759092104349221</v>
@@ -16692,7 +16432,7 @@
         <v>0.7407389842816668</v>
       </c>
       <c r="CY43" t="n">
-        <v>0.7925899732992105</v>
+        <v>0.7925899732992103</v>
       </c>
       <c r="CZ43" t="n">
         <v>0.749864681275165</v>
@@ -16760,7 +16500,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8064776281041783</v>
+        <v>0.8064776281041784</v>
       </c>
       <c r="B44" t="n">
         <v>0.8909373459124519</v>
@@ -16793,10 +16533,10 @@
         <v>0.7940002187053253</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8418815936229734</v>
+        <v>0.8418815936229733</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8425611342697905</v>
+        <v>0.8425611342697904</v>
       </c>
       <c r="N44" t="n">
         <v>0.7957000641236254</v>
@@ -16820,10 +16560,10 @@
         <v>0.8131819561291947</v>
       </c>
       <c r="U44" t="n">
-        <v>0.7747970991869745</v>
+        <v>0.7747970991869746</v>
       </c>
       <c r="V44" t="n">
-        <v>0.838883914760387</v>
+        <v>0.8388839147603872</v>
       </c>
       <c r="W44" t="n">
         <v>0.8187273327747085</v>
@@ -16973,7 +16713,7 @@
         <v>0.8087246359834035</v>
       </c>
       <c r="BT44" t="n">
-        <v>0.8042496571067024</v>
+        <v>0.8042496571067025</v>
       </c>
       <c r="BU44" t="n">
         <v>0.7881582762932189</v>
@@ -16994,7 +16734,7 @@
         <v>0.7850448650127499</v>
       </c>
       <c r="CA44" t="n">
-        <v>0.805187232845208</v>
+        <v>0.8051872328452081</v>
       </c>
       <c r="CB44" t="n">
         <v>0.7938194311715416</v>
@@ -17030,7 +16770,7 @@
         <v>0.8545543706703183</v>
       </c>
       <c r="CM44" t="n">
-        <v>0.7815283434292684</v>
+        <v>0.7815283434292685</v>
       </c>
       <c r="CN44" t="n">
         <v>0.7957522844507114</v>
@@ -17048,7 +16788,7 @@
         <v>0.7994958074037589</v>
       </c>
       <c r="CS44" t="n">
-        <v>0.827661338299417</v>
+        <v>0.8276613382994169</v>
       </c>
       <c r="CT44" t="n">
         <v>0.8189902041734181</v>
@@ -17057,13 +16797,13 @@
         <v>0.8107688500888172</v>
       </c>
       <c r="CV44" t="n">
-        <v>0.7530023082079984</v>
+        <v>0.7530023082079986</v>
       </c>
       <c r="CW44" t="n">
-        <v>0.7641913456758458</v>
+        <v>0.7641913456758459</v>
       </c>
       <c r="CX44" t="n">
-        <v>0.7696244797061808</v>
+        <v>0.7696244797061805</v>
       </c>
       <c r="CY44" t="n">
         <v>0.8240514936842729</v>
@@ -17078,7 +16818,7 @@
         <v>0.8265067480664265</v>
       </c>
       <c r="DC44" t="n">
-        <v>0.8010541115670116</v>
+        <v>0.8010541115670113</v>
       </c>
       <c r="DD44" t="n">
         <v>0.7982511241656605</v>
@@ -17087,7 +16827,7 @@
         <v>0.7917996663953034</v>
       </c>
       <c r="DF44" t="n">
-        <v>0.7971220544118085</v>
+        <v>0.7971220544118087</v>
       </c>
       <c r="DG44" t="n">
         <v>0.7733395668948351</v>
@@ -17117,7 +16857,7 @@
         <v>0.7930553022778517</v>
       </c>
       <c r="DP44" t="n">
-        <v>0.7746569681282882</v>
+        <v>0.7746569681282881</v>
       </c>
       <c r="DQ44" t="n">
         <v>0.7654544682282126</v>
@@ -17167,7 +16907,7 @@
         <v>0.8230137029013973</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8695355641662219</v>
+        <v>0.8695355641662221</v>
       </c>
       <c r="M45" t="n">
         <v>0.8756303034473871</v>
@@ -17176,7 +16916,7 @@
         <v>0.8296378054360825</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8228907686792062</v>
+        <v>0.822890768679206</v>
       </c>
       <c r="P45" t="n">
         <v>0.8990598075724543</v>
@@ -17200,7 +16940,7 @@
         <v>0.8721573558547993</v>
       </c>
       <c r="W45" t="n">
-        <v>0.8478956661999963</v>
+        <v>0.8478956661999966</v>
       </c>
       <c r="X45" t="n">
         <v>0.8134940734051996</v>
@@ -17221,7 +16961,7 @@
         <v>0.8066137952259023</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.7857524952013234</v>
+        <v>0.7857524952013235</v>
       </c>
       <c r="AE45" t="n">
         <v>0.7858273881919626</v>
@@ -17266,7 +17006,7 @@
         <v>0.7833536422664572</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.7780007039829242</v>
+        <v>0.7780007039829241</v>
       </c>
       <c r="AT45" t="n">
         <v>0.8212834146432948</v>
@@ -17293,10 +17033,10 @@
         <v>0.873107426729768</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.7880936191487459</v>
+        <v>0.7880936191487461</v>
       </c>
       <c r="BC45" t="n">
-        <v>0.8240534738813678</v>
+        <v>0.824053473881368</v>
       </c>
       <c r="BD45" t="n">
         <v>0.8250806878453731</v>
@@ -17308,7 +17048,7 @@
         <v>0.7838782670302724</v>
       </c>
       <c r="BG45" t="n">
-        <v>0.7870301742854298</v>
+        <v>0.7870301742854297</v>
       </c>
       <c r="BH45" t="n">
         <v>0.7952684664035707</v>
@@ -17374,7 +17114,7 @@
         <v>0.8224144630191308</v>
       </c>
       <c r="CC45" t="n">
-        <v>0.8206748563837851</v>
+        <v>0.8206748563837853</v>
       </c>
       <c r="CD45" t="n">
         <v>0.8233596470907701</v>
@@ -17461,7 +17201,7 @@
         <v>0.8205919339706274</v>
       </c>
       <c r="DF45" t="n">
-        <v>0.8248228365650908</v>
+        <v>0.8248228365650906</v>
       </c>
       <c r="DG45" t="n">
         <v>0.8057733513453836</v>
@@ -17526,13 +17266,13 @@
         <v>0.8558283303656735</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8816572800840661</v>
+        <v>0.8816572800840662</v>
       </c>
       <c r="H46" t="n">
         <v>0.9114325326329971</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9133158569596015</v>
+        <v>0.9133158569596014</v>
       </c>
       <c r="J46" t="n">
         <v>0.8447107583691407</v>
@@ -17556,7 +17296,7 @@
         <v>0.9295173799886801</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8492089236363424</v>
+        <v>0.8492089236363425</v>
       </c>
       <c r="R46" t="n">
         <v>0.8759557595959844</v>
@@ -17619,7 +17359,7 @@
         <v>0.8794997889569054</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.8858010396204247</v>
+        <v>0.8858010396204246</v>
       </c>
       <c r="AM46" t="n">
         <v>0.8496393968953799</v>
@@ -17691,7 +17431,7 @@
         <v>0.641273314663714</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.8359825027556367</v>
+        <v>0.8359825027556368</v>
       </c>
       <c r="BK46" t="n">
         <v>0.8134287554408641</v>
@@ -17775,7 +17515,7 @@
         <v>0.8576322605066414</v>
       </c>
       <c r="CL46" t="n">
-        <v>0.9170881720074007</v>
+        <v>0.9170881720074006</v>
       </c>
       <c r="CM46" t="n">
         <v>0.8322933840144534</v>
@@ -17820,13 +17560,13 @@
         <v>0.8262504522317885</v>
       </c>
       <c r="DA46" t="n">
-        <v>0.8655437172957547</v>
+        <v>0.8655437172957546</v>
       </c>
       <c r="DB46" t="n">
         <v>0.8894676359069346</v>
       </c>
       <c r="DC46" t="n">
-        <v>0.8657875141591743</v>
+        <v>0.8657875141591745</v>
       </c>
       <c r="DD46" t="n">
         <v>0.8604340722427321</v>
@@ -17903,10 +17643,10 @@
         <v>0.9056371157606509</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9432807949935019</v>
+        <v>0.9432807949935021</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9375394767757285</v>
+        <v>0.9375394767757284</v>
       </c>
       <c r="J47" t="n">
         <v>0.8730824766437</v>
@@ -17924,7 +17664,7 @@
         <v>0.9009212650627195</v>
       </c>
       <c r="O47" t="n">
-        <v>0.8770833833812858</v>
+        <v>0.8770833833812859</v>
       </c>
       <c r="P47" t="n">
         <v>0.9576234147624968</v>
@@ -17933,7 +17673,7 @@
         <v>0.8715313450129751</v>
       </c>
       <c r="R47" t="n">
-        <v>0.9052672091493885</v>
+        <v>0.9052672091493886</v>
       </c>
       <c r="S47" t="n">
         <v>0.8888709078393946</v>
@@ -17996,10 +17736,10 @@
         <v>0.921988927522894</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.8824343020602725</v>
+        <v>0.8824343020602726</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.8991753239360379</v>
+        <v>0.8991753239360378</v>
       </c>
       <c r="AO47" t="n">
         <v>0.9038282696356039</v>
@@ -18008,16 +17748,16 @@
         <v>0.9335966142953448</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.8622974469930988</v>
+        <v>0.8622974469930991</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.8499999103109791</v>
+        <v>0.8499999103109789</v>
       </c>
       <c r="AS47" t="n">
         <v>0.8465590619553083</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.8903523763954321</v>
+        <v>0.890352376395432</v>
       </c>
       <c r="AU47" t="n">
         <v>0.8379760159983645</v>
@@ -18035,7 +17775,7 @@
         <v>0.9206615623625838</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.8633532244392768</v>
+        <v>0.8633532244392769</v>
       </c>
       <c r="BA47" t="n">
         <v>0.9467994481028207</v>
@@ -18134,7 +17874,7 @@
         <v>0.8900698480474485</v>
       </c>
       <c r="CG47" t="n">
-        <v>0.8813535089237852</v>
+        <v>0.8813535089237853</v>
       </c>
       <c r="CH47" t="n">
         <v>0.9086213976459375</v>
@@ -18191,7 +17931,7 @@
         <v>0.9149076252381932</v>
       </c>
       <c r="CZ47" t="n">
-        <v>0.8546955048497739</v>
+        <v>0.8546955048497737</v>
       </c>
       <c r="DA47" t="n">
         <v>0.8972116950442343</v>
@@ -18248,7 +17988,7 @@
         <v>0.9111903333380289</v>
       </c>
       <c r="DS47" t="n">
-        <v>0.9045677577360587</v>
+        <v>0.9045677577360589</v>
       </c>
       <c r="DT47" t="n">
         <v>0.8436341295855152</v>
@@ -18328,13 +18068,13 @@
         <v>0.9066188482403715</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.9261925531359517</v>
+        <v>0.9261925531359516</v>
       </c>
       <c r="Z48" t="n">
         <v>0.9139630063702725</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.9274421583661152</v>
+        <v>0.927442158366115</v>
       </c>
       <c r="AB48" t="n">
         <v>0.9668369481316933</v>
@@ -18358,7 +18098,7 @@
         <v>0.9202398102218275</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.9341068478825072</v>
+        <v>0.9341068478825073</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.8919819096386087</v>
@@ -18421,7 +18161,7 @@
         <v>0.920204454461469</v>
       </c>
       <c r="BD48" t="n">
-        <v>0.936420787424969</v>
+        <v>0.9364207874249688</v>
       </c>
       <c r="BE48" t="n">
         <v>0.9257816104153633</v>
@@ -18511,7 +18251,7 @@
         <v>0.914612870057442</v>
       </c>
       <c r="CH48" t="n">
-        <v>0.9433131388770196</v>
+        <v>0.9433131388770197</v>
       </c>
       <c r="CI48" t="n">
         <v>0.9121550873188952</v>
@@ -18523,7 +18263,7 @@
         <v>0.9192491359749128</v>
       </c>
       <c r="CL48" t="n">
-        <v>0.9672103466163122</v>
+        <v>0.9672103466163121</v>
       </c>
       <c r="CM48" t="n">
         <v>0.8910873877845209</v>
@@ -18544,25 +18284,25 @@
         <v>0.9393966045212734</v>
       </c>
       <c r="CS48" t="n">
-        <v>0.9496100828981467</v>
+        <v>0.9496100828981469</v>
       </c>
       <c r="CT48" t="n">
-        <v>0.9574800647289509</v>
+        <v>0.957480064728951</v>
       </c>
       <c r="CU48" t="n">
-        <v>0.9399908230935378</v>
+        <v>0.9399908230935379</v>
       </c>
       <c r="CV48" t="n">
         <v>0.8754775566226605</v>
       </c>
       <c r="CW48" t="n">
-        <v>0.8677204524991906</v>
+        <v>0.8677204524991907</v>
       </c>
       <c r="CX48" t="n">
         <v>0.9051811143590958</v>
       </c>
       <c r="CY48" t="n">
-        <v>0.9402261046256599</v>
+        <v>0.9402261046256598</v>
       </c>
       <c r="CZ48" t="n">
         <v>0.8825337268876461</v>
@@ -18699,7 +18439,7 @@
         <v>0.9856242515641783</v>
       </c>
       <c r="X49" t="n">
-        <v>0.9377545990986333</v>
+        <v>0.9377545990986335</v>
       </c>
       <c r="Y49" t="n">
         <v>0.957120768697332</v>
@@ -18711,10 +18451,10 @@
         <v>0.9635754392896805</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.9909371674612214</v>
+        <v>0.9909371674612213</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.932895501411808</v>
+        <v>0.9328955014118081</v>
       </c>
       <c r="AD49" t="n">
         <v>0.9233079965746079</v>
@@ -18738,10 +18478,10 @@
         <v>0.9277578728983862</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.9557643681494337</v>
+        <v>0.9557643681494334</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.9841217195754919</v>
+        <v>0.984121719575492</v>
       </c>
       <c r="AM49" t="n">
         <v>0.9469758778202418</v>
@@ -18771,7 +18511,7 @@
         <v>0.8936286470074208</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.9632291382243016</v>
+        <v>0.9632291382243017</v>
       </c>
       <c r="AW49" t="n">
         <v>0.9142949603062814</v>
@@ -18798,7 +18538,7 @@
         <v>0.9701382618212726</v>
       </c>
       <c r="BE49" t="n">
-        <v>0.9533027416312001</v>
+        <v>0.9533027416312</v>
       </c>
       <c r="BF49" t="n">
         <v>0.8930544759168945</v>
@@ -18807,7 +18547,7 @@
         <v>0.8988649180951439</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.9363045606202399</v>
+        <v>0.93630456062024</v>
       </c>
       <c r="BI49" t="n">
         <v>0.6607466404600659</v>
@@ -18825,7 +18565,7 @@
         <v>0.9737920116859591</v>
       </c>
       <c r="BN49" t="n">
-        <v>0.9429506871529171</v>
+        <v>0.942950687152917</v>
       </c>
       <c r="BO49" t="n">
         <v>0.9447875414306672</v>
@@ -18843,7 +18583,7 @@
         <v>0.9795688690685994</v>
       </c>
       <c r="BT49" t="n">
-        <v>0.9422140310591895</v>
+        <v>0.9422140310591894</v>
       </c>
       <c r="BU49" t="n">
         <v>0.9590762422071587</v>
@@ -18864,7 +18604,7 @@
         <v>0.9429757457903364</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.9690996807461552</v>
+        <v>0.969099680746155</v>
       </c>
       <c r="CB49" t="n">
         <v>0.9349778821678606</v>
@@ -18891,7 +18631,7 @@
         <v>0.9421020117403573</v>
       </c>
       <c r="CJ49" t="n">
-        <v>0.9466392871167113</v>
+        <v>0.9466392871167114</v>
       </c>
       <c r="CK49" t="n">
         <v>0.9461517271219828</v>
@@ -18915,13 +18655,13 @@
         <v>0.9349429789661247</v>
       </c>
       <c r="CR49" t="n">
-        <v>0.9678954674927248</v>
+        <v>0.9678954674927247</v>
       </c>
       <c r="CS49" t="n">
         <v>0.975120455494774</v>
       </c>
       <c r="CT49" t="n">
-        <v>0.985533136938662</v>
+        <v>0.9855331369386621</v>
       </c>
       <c r="CU49" t="n">
         <v>0.9661079449681206</v>
@@ -18942,7 +18682,7 @@
         <v>0.9090567803738044</v>
       </c>
       <c r="DA49" t="n">
-        <v>0.9514603543203853</v>
+        <v>0.9514603543203852</v>
       </c>
       <c r="DB49" t="n">
         <v>0.9754511184459942</v>
@@ -18975,7 +18715,7 @@
         <v>0.946889799148579</v>
       </c>
       <c r="DL49" t="n">
-        <v>0.9531754255931175</v>
+        <v>0.9531754255931174</v>
       </c>
       <c r="DM49" t="n">
         <v>0.8993318990683679</v>
@@ -19046,7 +18786,7 @@
         <v>0.9908077973572034</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9682516996065756</v>
+        <v>0.9682516996065758</v>
       </c>
       <c r="P50" t="n">
         <v>1.018086752639439</v>
@@ -19064,7 +18804,7 @@
         <v>0.9711346436975906</v>
       </c>
       <c r="U50" t="n">
-        <v>0.9560694466628901</v>
+        <v>0.9560694466628902</v>
       </c>
       <c r="V50" t="n">
         <v>1.025149514483486</v>
@@ -19079,7 +18819,7 @@
         <v>0.9852728319373436</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.9733141487592973</v>
+        <v>0.9733141487592976</v>
       </c>
       <c r="AA50" t="n">
         <v>0.9957971555654688</v>
@@ -19091,10 +18831,10 @@
         <v>0.9589028641384585</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.9560463443191627</v>
+        <v>0.9560463443191629</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.9507699489403991</v>
+        <v>0.950769948940399</v>
       </c>
       <c r="AF50" t="n">
         <v>0.9748570936493429</v>
@@ -19112,13 +18852,13 @@
         <v>0.9603832746810427</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.9754268274520294</v>
+        <v>0.9754268274520291</v>
       </c>
       <c r="AL50" t="n">
         <v>1.005477125671997</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.9764570891962231</v>
+        <v>0.9764570891962232</v>
       </c>
       <c r="AN50" t="n">
         <v>0.9870971183914036</v>
@@ -19136,7 +18876,7 @@
         <v>0.9505357244173714</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.9583581762805086</v>
+        <v>0.9583581762805088</v>
       </c>
       <c r="AT50" t="n">
         <v>0.9772730973723888</v>
@@ -19172,7 +18912,7 @@
         <v>1.001579558466352</v>
       </c>
       <c r="BE50" t="n">
-        <v>0.9768327618502127</v>
+        <v>0.9768327618502128</v>
       </c>
       <c r="BF50" t="n">
         <v>0.9251170587359833</v>
@@ -19193,7 +18933,7 @@
         <v>0.968801697190804</v>
       </c>
       <c r="BL50" t="n">
-        <v>0.9905035987129726</v>
+        <v>0.9905035987129727</v>
       </c>
       <c r="BM50" t="n">
         <v>1.000209919203264</v>
@@ -19217,7 +18957,7 @@
         <v>1.007708605331695</v>
       </c>
       <c r="BT50" t="n">
-        <v>0.9631194302859397</v>
+        <v>0.9631194302859398</v>
       </c>
       <c r="BU50" t="n">
         <v>0.99236932447344</v>
@@ -19247,7 +18987,7 @@
         <v>0.927499389941267</v>
       </c>
       <c r="CD50" t="n">
-        <v>0.9754002632241378</v>
+        <v>0.9754002632241379</v>
       </c>
       <c r="CE50" t="n">
         <v>0.9533616361652608</v>
@@ -19277,7 +19017,7 @@
         <v>0.9458643361446323</v>
       </c>
       <c r="CN50" t="n">
-        <v>0.991444581700215</v>
+        <v>0.9914445817002151</v>
       </c>
       <c r="CO50" t="n">
         <v>0.9709452339833555</v>
@@ -19298,7 +19038,7 @@
         <v>1.005995303593844</v>
       </c>
       <c r="CU50" t="n">
-        <v>0.9875496755917007</v>
+        <v>0.9875496755917006</v>
       </c>
       <c r="CV50" t="n">
         <v>0.9398474808606138</v>
@@ -19367,7 +19107,7 @@
         <v>0.8473902773584566</v>
       </c>
       <c r="DR50" t="n">
-        <v>0.8964802420234983</v>
+        <v>0.8964802420234982</v>
       </c>
       <c r="DS50" t="n">
         <v>0.8940617131116315</v>
@@ -19384,7 +19124,7 @@
         <v>0.8557603618407706</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8660053748251649</v>
+        <v>0.8660053748251647</v>
       </c>
       <c r="D51" t="n">
         <v>0.8605987460349819</v>
@@ -19426,7 +19166,7 @@
         <v>1.025071050841282</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9699831709563158</v>
+        <v>0.9699831709563159</v>
       </c>
       <c r="R51" t="n">
         <v>0.9979790150755229</v>
@@ -19468,10 +19208,10 @@
         <v>0.9846925107963634</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.9799210636996346</v>
+        <v>0.9799210636996345</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.9978610568201138</v>
+        <v>0.9978610568201137</v>
       </c>
       <c r="AG51" t="n">
         <v>1.037224526648664</v>
@@ -19486,7 +19226,7 @@
         <v>0.9880055054467283</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.9929365334322626</v>
+        <v>0.9929365334322627</v>
       </c>
       <c r="AL51" t="n">
         <v>1.018110630259678</v>
@@ -19522,13 +19262,13 @@
         <v>1.013656622589157</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.966820778182821</v>
+        <v>0.9668207781828209</v>
       </c>
       <c r="AX51" t="n">
         <v>1.03768001090858</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.017890603852136</v>
+        <v>1.017890603852137</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.012706750651516</v>
@@ -19582,7 +19322,7 @@
         <v>1.024284672729517</v>
       </c>
       <c r="BQ51" t="n">
-        <v>0.9658064722620866</v>
+        <v>0.9658064722620865</v>
       </c>
       <c r="BR51" t="n">
         <v>0.9991972532193579</v>
@@ -19609,7 +19349,7 @@
         <v>0.9824059868630783</v>
       </c>
       <c r="BZ51" t="n">
-        <v>0.9934117422050831</v>
+        <v>0.993411742205083</v>
       </c>
       <c r="CA51" t="n">
         <v>1.008831310340811</v>
@@ -19675,7 +19415,7 @@
         <v>1.003557936358519</v>
       </c>
       <c r="CV51" t="n">
-        <v>0.9675346164120655</v>
+        <v>0.9675346164120657</v>
       </c>
       <c r="CW51" t="n">
         <v>0.9439335526328883</v>
@@ -19687,7 +19427,7 @@
         <v>0.9900636788001639</v>
       </c>
       <c r="CZ51" t="n">
-        <v>0.955443523076431</v>
+        <v>0.9554435230764309</v>
       </c>
       <c r="DA51" t="n">
         <v>0.9923979158392596</v>
@@ -19717,7 +19457,7 @@
         <v>0.9595425415157357</v>
       </c>
       <c r="DJ51" t="n">
-        <v>1.002083697965117</v>
+        <v>1.002083697965116</v>
       </c>
       <c r="DK51" t="n">
         <v>0.997759269046776</v>
@@ -19726,16 +19466,16 @@
         <v>0.9880374377521581</v>
       </c>
       <c r="DM51" t="n">
-        <v>0.9520393714215182</v>
+        <v>0.9520393714215181</v>
       </c>
       <c r="DN51" t="n">
-        <v>0.9975425575251967</v>
+        <v>0.9975425575251966</v>
       </c>
       <c r="DO51" t="n">
         <v>0.9916748823178519</v>
       </c>
       <c r="DP51" t="n">
-        <v>0.9404464301178512</v>
+        <v>0.9404464301178511</v>
       </c>
       <c r="DQ51" t="n">
         <v>0.8575912537274616</v>
@@ -19890,7 +19630,7 @@
         <v>1.009762193620104</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.9755635385726958</v>
+        <v>0.975563538572696</v>
       </c>
       <c r="AV52" t="n">
         <v>1.027929504012743</v>
@@ -19962,10 +19702,10 @@
         <v>1.01538349891982</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.038388944578991</v>
+        <v>1.03838894457899</v>
       </c>
       <c r="BT52" t="n">
-        <v>0.9928503945391939</v>
+        <v>0.992850394539194</v>
       </c>
       <c r="BU52" t="n">
         <v>1.042387169632405</v>
@@ -19974,7 +19714,7 @@
         <v>1.049764525503479</v>
       </c>
       <c r="BW52" t="n">
-        <v>0.9732598721018039</v>
+        <v>0.973259872101804</v>
       </c>
       <c r="BX52" t="n">
         <v>1.026616056910478</v>
@@ -20043,7 +19783,7 @@
         <v>1.020866910890417</v>
       </c>
       <c r="CT52" t="n">
-        <v>1.016244730826714</v>
+        <v>1.016244730826715</v>
       </c>
       <c r="CU52" t="n">
         <v>1.013250245553546</v>
@@ -20097,7 +19837,7 @@
         <v>1.014754233754909</v>
       </c>
       <c r="DL52" t="n">
-        <v>0.9960329772674373</v>
+        <v>0.9960329772674374</v>
       </c>
       <c r="DM52" t="n">
         <v>0.9752063572946874</v>
@@ -20141,7 +19881,7 @@
         <v>0.8452916733010979</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9264623726804385</v>
+        <v>0.9264623726804384</v>
       </c>
       <c r="G53" t="n">
         <v>0.9990022638182702</v>
@@ -20408,7 +20148,7 @@
         <v>1.008830856470099</v>
       </c>
       <c r="CQ53" t="n">
-        <v>1.032081769544262</v>
+        <v>1.032081769544261</v>
       </c>
       <c r="CR53" t="n">
         <v>1.021906298760374</v>
@@ -20426,7 +20166,7 @@
         <v>1.006041822692794</v>
       </c>
       <c r="CW53" t="n">
-        <v>0.9694527243517299</v>
+        <v>0.9694527243517298</v>
       </c>
       <c r="CX53" t="n">
         <v>1.022624993887376</v>
@@ -20435,7 +20175,7 @@
         <v>0.9901699328603824</v>
       </c>
       <c r="CZ53" t="n">
-        <v>0.9844964305142915</v>
+        <v>0.9844964305142916</v>
       </c>
       <c r="DA53" t="n">
         <v>1.017684514389119</v>
@@ -20462,7 +20202,7 @@
         <v>1.006255516590909</v>
       </c>
       <c r="DI53" t="n">
-        <v>0.9627950778517326</v>
+        <v>0.9627950778517324</v>
       </c>
       <c r="DJ53" t="n">
         <v>1.01246086524884</v>
@@ -20474,7 +20214,7 @@
         <v>0.9964800135285399</v>
       </c>
       <c r="DM53" t="n">
-        <v>0.9938247491847666</v>
+        <v>0.9938247491847668</v>
       </c>
       <c r="DN53" t="n">
         <v>1.0333597149636</v>
@@ -20483,7 +20223,7 @@
         <v>1.008135646234563</v>
       </c>
       <c r="DP53" t="n">
-        <v>0.9816668714221716</v>
+        <v>0.9816668714221713</v>
       </c>
       <c r="DQ53" t="n">
         <v>0.8760510110284968</v>
@@ -20515,7 +20255,7 @@
         <v>0.8573993132932625</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9319729732274278</v>
+        <v>0.9319729732274279</v>
       </c>
       <c r="G54" t="n">
         <v>1.0000951160777</v>
@@ -20584,10 +20324,10 @@
         <v>1.013929099148464</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.012117691523154</v>
+        <v>1.012117691523155</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.028275995327963</v>
+        <v>1.028275995327962</v>
       </c>
       <c r="AE54" t="n">
         <v>1.030226464838661</v>
@@ -20638,7 +20378,7 @@
         <v>1.013200453823785</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.012272193677246</v>
+        <v>1.012272193677245</v>
       </c>
       <c r="AV54" t="n">
         <v>1.027816941838782</v>
@@ -20674,13 +20414,13 @@
         <v>1.010502413947506</v>
       </c>
       <c r="BG54" t="n">
-        <v>0.9947915989215484</v>
+        <v>0.9947915989215486</v>
       </c>
       <c r="BH54" t="n">
         <v>1.066076597132008</v>
       </c>
       <c r="BI54" t="n">
-        <v>0.8004227317178152</v>
+        <v>0.8004227317178154</v>
       </c>
       <c r="BJ54" t="n">
         <v>1.001770256720482</v>
@@ -20740,7 +20480,7 @@
         <v>0.9893775129660564</v>
       </c>
       <c r="CC54" t="n">
-        <v>0.961991897903031</v>
+        <v>0.9619918979030311</v>
       </c>
       <c r="CD54" t="n">
         <v>1.01124255935329</v>
@@ -20937,7 +20677,7 @@
         <v>1.048093689298232</v>
       </c>
       <c r="V55" t="n">
-        <v>1.003979462579082</v>
+        <v>1.003979462579081</v>
       </c>
       <c r="W55" t="n">
         <v>1.038321998438961</v>
@@ -21009,7 +20749,7 @@
         <v>1.074170321307457</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.002727476867389</v>
+        <v>1.002727476867388</v>
       </c>
       <c r="AU55" t="n">
         <v>1.019862206249846</v>
@@ -21087,7 +20827,7 @@
         <v>1.004082003633234</v>
       </c>
       <c r="BT55" t="n">
-        <v>0.9768835173042584</v>
+        <v>0.9768835173042586</v>
       </c>
       <c r="BU55" t="n">
         <v>1.043080086647146</v>
@@ -21108,7 +20848,7 @@
         <v>1.017191910608009</v>
       </c>
       <c r="CA55" t="n">
-        <v>0.9785563274687111</v>
+        <v>0.978556327468711</v>
       </c>
       <c r="CB55" t="n">
         <v>0.9765014578236419</v>
@@ -21138,7 +20878,7 @@
         <v>0.997887435564897</v>
       </c>
       <c r="CK55" t="n">
-        <v>0.9895524835820495</v>
+        <v>0.9895524835820494</v>
       </c>
       <c r="CL55" t="n">
         <v>0.9824097520562194</v>
@@ -21201,13 +20941,13 @@
         <v>0.9942918441868605</v>
       </c>
       <c r="DF55" t="n">
-        <v>0.9822909894239965</v>
+        <v>0.9822909894239967</v>
       </c>
       <c r="DG55" t="n">
         <v>1.00198098218409</v>
       </c>
       <c r="DH55" t="n">
-        <v>0.9655637128050889</v>
+        <v>0.9655637128050888</v>
       </c>
       <c r="DI55" t="n">
         <v>0.9316470156084371</v>
@@ -21329,7 +21069,7 @@
         <v>1.03837431150718</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.955163006654843</v>
+        <v>0.9551630066548428</v>
       </c>
       <c r="AC56" t="n">
         <v>0.9917564008537061</v>
@@ -21404,7 +21144,7 @@
         <v>1.048855339690232</v>
       </c>
       <c r="BA56" t="n">
-        <v>0.8678558969514952</v>
+        <v>0.867855896951495</v>
       </c>
       <c r="BB56" t="n">
         <v>1.000157319101864</v>
@@ -21431,7 +21171,7 @@
         <v>0.8725164236642992</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.9734471805374828</v>
+        <v>0.9734471805374826</v>
       </c>
       <c r="BK56" t="n">
         <v>1.066564552471801</v>
@@ -21440,7 +21180,7 @@
         <v>1.024304127502882</v>
       </c>
       <c r="BM56" t="n">
-        <v>0.9884226702530148</v>
+        <v>0.9884226702530146</v>
       </c>
       <c r="BN56" t="n">
         <v>0.9585867558293165</v>
@@ -21449,16 +21189,16 @@
         <v>1.028252764404151</v>
       </c>
       <c r="BP56" t="n">
-        <v>0.9790767546990218</v>
+        <v>0.9790767546990219</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0.9898551149452781</v>
+        <v>0.989855114945278</v>
       </c>
       <c r="BR56" t="n">
         <v>0.9856933279155838</v>
       </c>
       <c r="BS56" t="n">
-        <v>0.9691206321157887</v>
+        <v>0.9691206321157886</v>
       </c>
       <c r="BT56" t="n">
         <v>0.9491015392684606</v>
@@ -21506,13 +21246,13 @@
         <v>0.953162086931737</v>
       </c>
       <c r="CI56" t="n">
-        <v>0.9726002254505748</v>
+        <v>0.9726002254505747</v>
       </c>
       <c r="CJ56" t="n">
         <v>0.9811404238316436</v>
       </c>
       <c r="CK56" t="n">
-        <v>0.9709058487550677</v>
+        <v>0.9709058487550676</v>
       </c>
       <c r="CL56" t="n">
         <v>0.9530390812455312</v>
@@ -21527,13 +21267,13 @@
         <v>0.95773462294446</v>
       </c>
       <c r="CP56" t="n">
-        <v>0.9603984906814137</v>
+        <v>0.9603984906814138</v>
       </c>
       <c r="CQ56" t="n">
         <v>1.009025980389094</v>
       </c>
       <c r="CR56" t="n">
-        <v>0.9678842731599031</v>
+        <v>0.9678842731599033</v>
       </c>
       <c r="CS56" t="n">
         <v>0.9697471641935758</v>
@@ -21542,7 +21282,7 @@
         <v>0.8866664278301799</v>
       </c>
       <c r="CU56" t="n">
-        <v>0.9673588386076258</v>
+        <v>0.9673588386076259</v>
       </c>
       <c r="CV56" t="n">
         <v>0.9995827546901835</v>
@@ -21566,13 +21306,13 @@
         <v>0.9166922793685806</v>
       </c>
       <c r="DC56" t="n">
-        <v>0.9846156219165033</v>
+        <v>0.9846156219165035</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.9519747309401239</v>
+        <v>0.9519747309401236</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.9717370180297406</v>
+        <v>0.9717370180297404</v>
       </c>
       <c r="DF56" t="n">
         <v>0.9563053473172067</v>
@@ -21581,13 +21321,13 @@
         <v>0.9790654269244022</v>
       </c>
       <c r="DH56" t="n">
-        <v>0.9249525750721139</v>
+        <v>0.924952575072114</v>
       </c>
       <c r="DI56" t="n">
         <v>0.9000177101025305</v>
       </c>
       <c r="DJ56" t="n">
-        <v>0.9600388275079117</v>
+        <v>0.9600388275079116</v>
       </c>
       <c r="DK56" t="n">
         <v>0.9936836262017248</v>
@@ -21614,7 +21354,7 @@
         <v>0.8360140495261688</v>
       </c>
       <c r="DS56" t="n">
-        <v>0.8953121820965007</v>
+        <v>0.8953121820965008</v>
       </c>
       <c r="DT56" t="n">
         <v>0.9228918826852234</v>
@@ -21697,7 +21437,7 @@
         <v>0.9741802713288937</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.9249977949933443</v>
+        <v>0.9249977949933444</v>
       </c>
       <c r="AA57" t="n">
         <v>1.010792929041735</v>
@@ -21748,7 +21488,7 @@
         <v>0.9137593322041074</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.9571482951745732</v>
+        <v>0.9571482951745731</v>
       </c>
       <c r="AR57" t="n">
         <v>0.9825849783155695</v>
@@ -21772,7 +21512,7 @@
         <v>1.038818635801637</v>
       </c>
       <c r="AY57" t="n">
-        <v>0.9354397331838794</v>
+        <v>0.9354397331838793</v>
       </c>
       <c r="AZ57" t="n">
         <v>1.023492751439391</v>
@@ -21826,7 +21566,7 @@
         <v>0.9337507019057486</v>
       </c>
       <c r="BQ57" t="n">
-        <v>0.9660387596865845</v>
+        <v>0.9660387596865844</v>
       </c>
       <c r="BR57" t="n">
         <v>0.9498630778250516</v>
@@ -21859,7 +21599,7 @@
         <v>0.8881049661229536</v>
       </c>
       <c r="CB57" t="n">
-        <v>0.9199140297844479</v>
+        <v>0.919914029784448</v>
       </c>
       <c r="CC57" t="n">
         <v>0.9314446037878247</v>
@@ -21892,10 +21632,10 @@
         <v>0.9128984583929582</v>
       </c>
       <c r="CM57" t="n">
-        <v>0.9758078889330234</v>
+        <v>0.9758078889330236</v>
       </c>
       <c r="CN57" t="n">
-        <v>0.983861299037931</v>
+        <v>0.9838612990379308</v>
       </c>
       <c r="CO57" t="n">
         <v>0.9170911957586804</v>
@@ -21913,7 +21653,7 @@
         <v>0.9306535008246778</v>
       </c>
       <c r="CT57" t="n">
-        <v>0.8175060387280966</v>
+        <v>0.8175060387280965</v>
       </c>
       <c r="CU57" t="n">
         <v>0.9293304701005115</v>
@@ -21955,7 +21695,7 @@
         <v>0.9441890372046274</v>
       </c>
       <c r="DH57" t="n">
-        <v>0.8683983280328077</v>
+        <v>0.8683983280328076</v>
       </c>
       <c r="DI57" t="n">
         <v>0.8551118766796474</v>
@@ -22002,7 +21742,7 @@
         <v>0.8726244736678971</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9202089342369062</v>
+        <v>0.9202089342369064</v>
       </c>
       <c r="D58" t="n">
         <v>0.8687845888750083</v>
@@ -22023,19 +21763,19 @@
         <v>0.8213669688267778</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9450747465207359</v>
+        <v>0.9450747465207358</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9674730364635872</v>
+        <v>0.9674730364635871</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9679617285185095</v>
+        <v>0.9679617285185094</v>
       </c>
       <c r="M58" t="n">
         <v>0.884024190806144</v>
       </c>
       <c r="N58" t="n">
-        <v>0.9657686083450716</v>
+        <v>0.9657686083450715</v>
       </c>
       <c r="O58" t="n">
         <v>0.9338220136057968</v>
@@ -22071,7 +21811,7 @@
         <v>0.9277232886980745</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.8682693904634365</v>
+        <v>0.8682693904634364</v>
       </c>
       <c r="AA58" t="n">
         <v>0.9714997997289202</v>
@@ -22083,7 +21823,7 @@
         <v>0.9299875330406604</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.9484034200518995</v>
+        <v>0.9484034200518994</v>
       </c>
       <c r="AE58" t="n">
         <v>0.9551566783790607</v>
@@ -22095,7 +21835,7 @@
         <v>0.8748353330706029</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.9517064384193415</v>
+        <v>0.9517064384193417</v>
       </c>
       <c r="AI58" t="n">
         <v>0.9625202487388924</v>
@@ -22119,7 +21859,7 @@
         <v>0.8988059399849332</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.8577264812231185</v>
+        <v>0.8577264812231186</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.9148450577667674</v>
@@ -22140,7 +21880,7 @@
         <v>0.8927939309520889</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.970234530398041</v>
+        <v>0.9702345303980411</v>
       </c>
       <c r="AX58" t="n">
         <v>1.000690028195821</v>
@@ -22197,7 +21937,7 @@
         <v>0.9674669998188927</v>
       </c>
       <c r="BP58" t="n">
-        <v>0.8749140701598339</v>
+        <v>0.8749140701598341</v>
       </c>
       <c r="BQ58" t="n">
         <v>0.9311668831793077</v>
@@ -22218,7 +21958,7 @@
         <v>0.8963309693652584</v>
       </c>
       <c r="BW58" t="n">
-        <v>0.889620672381116</v>
+        <v>0.8896206723811161</v>
       </c>
       <c r="BX58" t="n">
         <v>0.9029069413729159</v>
@@ -22260,7 +22000,7 @@
         <v>0.9161875576041747</v>
       </c>
       <c r="CK58" t="n">
-        <v>0.9016199108059036</v>
+        <v>0.9016199108059038</v>
       </c>
       <c r="CL58" t="n">
         <v>0.8606671498325749</v>
@@ -22275,7 +22015,7 @@
         <v>0.8626738071953122</v>
       </c>
       <c r="CP58" t="n">
-        <v>0.872960699138028</v>
+        <v>0.8729606991380279</v>
       </c>
       <c r="CQ58" t="n">
         <v>0.9362427086853075</v>
@@ -22308,7 +22048,7 @@
         <v>0.8950208978081056</v>
       </c>
       <c r="DA58" t="n">
-        <v>0.9472186758651439</v>
+        <v>0.9472186758651437</v>
       </c>
       <c r="DB58" t="n">
         <v>0.7926678020368784</v>
@@ -22344,10 +22084,10 @@
         <v>0.8512833827992388</v>
       </c>
       <c r="DM58" t="n">
-        <v>0.9565490646740384</v>
+        <v>0.9565490646740383</v>
       </c>
       <c r="DN58" t="n">
-        <v>0.9632131514050498</v>
+        <v>0.9632131514050499</v>
       </c>
       <c r="DO58" t="n">
         <v>0.8540702449391786</v>
@@ -22365,12 +22105,12 @@
         <v>0.8956060123054744</v>
       </c>
       <c r="DT58" t="n">
-        <v>0.9259443718871393</v>
+        <v>0.9259443718871392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.8182531773365374</v>
+        <v>0.8182531773365371</v>
       </c>
       <c r="B59" t="n">
         <v>0.8757061389535532</v>
@@ -22430,13 +22170,13 @@
         <v>0.7804501088804577</v>
       </c>
       <c r="U59" t="n">
-        <v>0.9356233215281804</v>
+        <v>0.9356233215281805</v>
       </c>
       <c r="V59" t="n">
         <v>0.7840617376796489</v>
       </c>
       <c r="W59" t="n">
-        <v>0.8340343384122801</v>
+        <v>0.83403433841228</v>
       </c>
       <c r="X59" t="n">
         <v>0.8753641263658144</v>
@@ -22457,7 +22197,7 @@
         <v>0.880769374907116</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.8998779168711225</v>
+        <v>0.8998779168711227</v>
       </c>
       <c r="AE59" t="n">
         <v>0.905029452355865</v>
@@ -22472,7 +22212,7 @@
         <v>0.8940775165176827</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.9123898514956046</v>
+        <v>0.9123898514956045</v>
       </c>
       <c r="AJ59" t="n">
         <v>0.8382271534958815</v>
@@ -22481,7 +22221,7 @@
         <v>0.952360274888894</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.7300280565301016</v>
+        <v>0.7300280565301018</v>
       </c>
       <c r="AM59" t="n">
         <v>0.8706263241675369</v>
@@ -22502,7 +22242,7 @@
         <v>0.90184310564843</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.9800168388260059</v>
+        <v>0.9800168388260061</v>
       </c>
       <c r="AT59" t="n">
         <v>0.8623238598176012</v>
@@ -22538,7 +22278,7 @@
         <v>0.9141409448546133</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.7573574736328186</v>
+        <v>0.7573574736328185</v>
       </c>
       <c r="BF59" t="n">
         <v>0.8963688325680534</v>
@@ -22550,7 +22290,7 @@
         <v>0.9408166920981492</v>
       </c>
       <c r="BI59" t="n">
-        <v>0.9736191773050643</v>
+        <v>0.9736191773050641</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.8382544136151863</v>
@@ -22580,7 +22320,7 @@
         <v>0.8369026741901758</v>
       </c>
       <c r="BS59" t="n">
-        <v>0.7791551141130483</v>
+        <v>0.7791551141130484</v>
       </c>
       <c r="BT59" t="n">
         <v>0.7807056256807683</v>
@@ -22598,7 +22338,7 @@
         <v>0.8430449817099321</v>
       </c>
       <c r="BY59" t="n">
-        <v>0.8374460447926995</v>
+        <v>0.8374460447926996</v>
       </c>
       <c r="BZ59" t="n">
         <v>0.8698265377984242</v>
@@ -22631,7 +22371,7 @@
         <v>0.8435531886878446</v>
       </c>
       <c r="CJ59" t="n">
-        <v>0.8639708103489258</v>
+        <v>0.8639708103489259</v>
       </c>
       <c r="CK59" t="n">
         <v>0.8466987173967877</v>
@@ -22673,7 +22413,7 @@
         <v>0.8359398830617208</v>
       </c>
       <c r="CX59" t="n">
-        <v>0.9043524585672074</v>
+        <v>0.9043524585672075</v>
       </c>
       <c r="CY59" t="n">
         <v>0.7302466180046318</v>
@@ -22739,7 +22479,7 @@
         <v>0.8952879265817942</v>
       </c>
       <c r="DT59" t="n">
-        <v>0.9260132315854247</v>
+        <v>0.9260132315854246</v>
       </c>
     </row>
     <row r="60">
@@ -22756,7 +22496,7 @@
         <v>0.8825052850295841</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9642718213781605</v>
+        <v>0.9642718213781607</v>
       </c>
       <c r="F60" t="n">
         <v>0.8820516263665453</v>
@@ -22819,7 +22559,7 @@
         <v>0.792557160024128</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.7034305192004039</v>
+        <v>0.7034305192004037</v>
       </c>
       <c r="AA60" t="n">
         <v>0.8533562316629052</v>
@@ -22831,7 +22571,7 @@
         <v>0.8171396437814837</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.8374175745339617</v>
+        <v>0.8374175745339615</v>
       </c>
       <c r="AE60" t="n">
         <v>0.8404511242454457</v>
@@ -22873,7 +22613,7 @@
         <v>0.7812697411833079</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.8413542788113344</v>
+        <v>0.8413542788113342</v>
       </c>
       <c r="AS60" t="n">
         <v>0.9213638823434571</v>
@@ -22915,7 +22655,7 @@
         <v>0.6621507118334061</v>
       </c>
       <c r="BF60" t="n">
-        <v>0.8337265685697387</v>
+        <v>0.8337265685697389</v>
       </c>
       <c r="BG60" t="n">
         <v>0.7732619592929615</v>
@@ -22933,7 +22673,7 @@
         <v>0.8884856480228213</v>
       </c>
       <c r="BL60" t="n">
-        <v>0.8237489651715706</v>
+        <v>0.8237489651715705</v>
       </c>
       <c r="BM60" t="n">
         <v>0.7360258207961371</v>
@@ -22963,10 +22703,10 @@
         <v>0.8130359510666308</v>
       </c>
       <c r="BV60" t="n">
-        <v>0.7344638643593306</v>
+        <v>0.7344638643593305</v>
       </c>
       <c r="BW60" t="n">
-        <v>0.7500022248952356</v>
+        <v>0.7500022248952354</v>
       </c>
       <c r="BX60" t="n">
         <v>0.7689757404836199</v>
@@ -22996,7 +22736,7 @@
         <v>0.8008395254189569</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.8268688735031027</v>
+        <v>0.8268688735031026</v>
       </c>
       <c r="CH60" t="n">
         <v>0.6645407433175439</v>
@@ -23089,7 +22829,7 @@
         <v>0.7922393791271799</v>
       </c>
       <c r="DL60" t="n">
-        <v>0.7014759396993254</v>
+        <v>0.7014759396993255</v>
       </c>
       <c r="DM60" t="n">
         <v>0.8617314686464557</v>
@@ -23130,7 +22870,7 @@
         <v>0.8908968160605802</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9744005772474919</v>
+        <v>0.9744005772474917</v>
       </c>
       <c r="F61" t="n">
         <v>0.8470908929213599</v>
@@ -23145,13 +22885,13 @@
         <v>0.5254585179454677</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7433472696306962</v>
+        <v>0.743347269630696</v>
       </c>
       <c r="K61" t="n">
         <v>0.7563293217383733</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8112596003176079</v>
+        <v>0.811259600317608</v>
       </c>
       <c r="M61" t="n">
         <v>0.6460791853484033</v>
@@ -23232,7 +22972,7 @@
         <v>0.5222944019090304</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.7060675176325982</v>
+        <v>0.706067517632598</v>
       </c>
       <c r="AN61" t="n">
         <v>0.8053706973238085</v>
@@ -23265,7 +23005,7 @@
         <v>0.8200333793993756</v>
       </c>
       <c r="AX61" t="n">
-        <v>0.8360915140831909</v>
+        <v>0.8360915140831908</v>
       </c>
       <c r="AY61" t="n">
         <v>0.6394427553185252</v>
@@ -23277,7 +23017,7 @@
         <v>0.3489756705601045</v>
       </c>
       <c r="BB61" t="n">
-        <v>0.6897306274854238</v>
+        <v>0.6897306274854236</v>
       </c>
       <c r="BC61" t="n">
         <v>0.6374035525360774</v>
@@ -23316,7 +23056,7 @@
         <v>0.6106716700060399</v>
       </c>
       <c r="BO61" t="n">
-        <v>0.7722995903116779</v>
+        <v>0.7722995903116777</v>
       </c>
       <c r="BP61" t="n">
         <v>0.6117949646874714</v>
@@ -23334,7 +23074,7 @@
         <v>0.5863282588317694</v>
       </c>
       <c r="BU61" t="n">
-        <v>0.7278008791632659</v>
+        <v>0.7278008791632656</v>
       </c>
       <c r="BV61" t="n">
         <v>0.6306745000551452</v>
@@ -23349,7 +23089,7 @@
         <v>0.6624119996665113</v>
       </c>
       <c r="BZ61" t="n">
-        <v>0.7107529560472379</v>
+        <v>0.7107529560472381</v>
       </c>
       <c r="CA61" t="n">
         <v>0.5346981921173208</v>
@@ -23364,7 +23104,7 @@
         <v>0.6861726773095226</v>
       </c>
       <c r="CE61" t="n">
-        <v>0.696446978564541</v>
+        <v>0.6964469785645409</v>
       </c>
       <c r="CF61" t="n">
         <v>0.7191813163577206</v>
@@ -23373,7 +23113,7 @@
         <v>0.7476398747075326</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.5569293957871887</v>
+        <v>0.5569293957871888</v>
       </c>
       <c r="CI61" t="n">
         <v>0.6828434183914976</v>
@@ -23421,7 +23161,7 @@
         <v>0.6880278675912898</v>
       </c>
       <c r="CX61" t="n">
-        <v>0.7618610899098506</v>
+        <v>0.7618610899098507</v>
       </c>
       <c r="CY61" t="n">
         <v>0.5251911386639161</v>
@@ -23469,7 +23209,7 @@
         <v>0.7924362729649574</v>
       </c>
       <c r="DN61" t="n">
-        <v>0.779117433675777</v>
+        <v>0.7791174336757769</v>
       </c>
       <c r="DO61" t="n">
         <v>0.5851317444625731</v>
@@ -23504,7 +23244,7 @@
         <v>0.8998100654787429</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9784848159859555</v>
+        <v>0.9784848159859553</v>
       </c>
       <c r="F62" t="n">
         <v>0.8003107813494315</v>
@@ -23516,7 +23256,7 @@
         <v>0.5949708101847044</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4123221155261247</v>
+        <v>0.4123221155261248</v>
       </c>
       <c r="J62" t="n">
         <v>0.6453733687128778</v>
@@ -23531,7 +23271,7 @@
         <v>0.5404781658977651</v>
       </c>
       <c r="N62" t="n">
-        <v>0.7063715317462608</v>
+        <v>0.706371531746261</v>
       </c>
       <c r="O62" t="n">
         <v>0.6263933777949326</v>
@@ -23543,7 +23283,7 @@
         <v>0.7184997022804634</v>
       </c>
       <c r="R62" t="n">
-        <v>0.6222936055442867</v>
+        <v>0.6222936055442868</v>
       </c>
       <c r="S62" t="n">
         <v>0.6690539120035311</v>
@@ -23567,7 +23307,7 @@
         <v>0.5997097431761064</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.4818575891663862</v>
+        <v>0.481857589166386</v>
       </c>
       <c r="AA62" t="n">
         <v>0.6771103244568522</v>
@@ -23642,7 +23382,7 @@
         <v>0.7619712049151111</v>
       </c>
       <c r="AY62" t="n">
-        <v>0.5333554269202654</v>
+        <v>0.5333554269202653</v>
       </c>
       <c r="AZ62" t="n">
         <v>0.6845728802864605</v>
@@ -23660,7 +23400,7 @@
         <v>0.6511163524029455</v>
       </c>
       <c r="BE62" t="n">
-        <v>0.4358962750415193</v>
+        <v>0.4358962750415192</v>
       </c>
       <c r="BF62" t="n">
         <v>0.6601699230993525</v>
@@ -23756,7 +23496,7 @@
         <v>0.6092431959915524</v>
       </c>
       <c r="CK62" t="n">
-        <v>0.5866178337629805</v>
+        <v>0.5866178337629806</v>
       </c>
       <c r="CL62" t="n">
         <v>0.5191531262863772</v>
@@ -23804,10 +23544,10 @@
         <v>0.5742441408839897</v>
       </c>
       <c r="DA62" t="n">
-        <v>0.6730026525304417</v>
+        <v>0.6730026525304418</v>
       </c>
       <c r="DB62" t="n">
-        <v>0.3826886936350056</v>
+        <v>0.3826886936350055</v>
       </c>
       <c r="DC62" t="n">
         <v>0.5750263182232016</v>
@@ -23840,7 +23580,7 @@
         <v>0.497012571846047</v>
       </c>
       <c r="DM62" t="n">
-        <v>0.7074667815234978</v>
+        <v>0.707466781523498</v>
       </c>
       <c r="DN62" t="n">
         <v>0.6907052965830757</v>
@@ -23869,7 +23609,7 @@
         <v>0.5559424583668739</v>
       </c>
       <c r="B63" t="n">
-        <v>0.8887210523269242</v>
+        <v>0.888721052326924</v>
       </c>
       <c r="C63" t="n">
         <v>0.9245277082090276</v>
@@ -23905,7 +23645,7 @@
         <v>0.4292608572170081</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6076218605560425</v>
+        <v>0.6076218605560424</v>
       </c>
       <c r="O63" t="n">
         <v>0.516090294332205</v>
@@ -23926,7 +23666,7 @@
         <v>0.3561842980611244</v>
       </c>
       <c r="U63" t="n">
-        <v>0.573575999907964</v>
+        <v>0.5735759999079639</v>
       </c>
       <c r="V63" t="n">
         <v>0.3591872986640697</v>
@@ -23980,7 +23720,7 @@
         <v>0.2974080515938557</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.4910103363456007</v>
+        <v>0.4910103363456006</v>
       </c>
       <c r="AN63" t="n">
         <v>0.6281874069010144</v>
@@ -24037,7 +23777,7 @@
         <v>0.3204750824939122</v>
       </c>
       <c r="BF63" t="n">
-        <v>0.5523836833261513</v>
+        <v>0.5523836833261514</v>
       </c>
       <c r="BG63" t="n">
         <v>0.4593184650919079</v>
@@ -24070,7 +23810,7 @@
         <v>0.3853780292184512</v>
       </c>
       <c r="BQ63" t="n">
-        <v>0.5435730576264087</v>
+        <v>0.5435730576264086</v>
       </c>
       <c r="BR63" t="n">
         <v>0.443464347932692</v>
@@ -24097,7 +23837,7 @@
         <v>0.4355846953417342</v>
       </c>
       <c r="BZ63" t="n">
-        <v>0.4991844507939252</v>
+        <v>0.4991844507939251</v>
       </c>
       <c r="CA63" t="n">
         <v>0.3105977228153416</v>
@@ -24127,7 +23867,7 @@
         <v>0.4667911231845814</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.4978866646883139</v>
+        <v>0.4978866646883138</v>
       </c>
       <c r="CK63" t="n">
         <v>0.4759917266110774</v>
@@ -24196,7 +23936,7 @@
         <v>0.3818686240552014</v>
       </c>
       <c r="DG63" t="n">
-        <v>0.4527901083696382</v>
+        <v>0.4527901083696381</v>
       </c>
       <c r="DH63" t="n">
         <v>0.2556348991392797</v>
@@ -24214,7 +23954,7 @@
         <v>0.3858630606220441</v>
       </c>
       <c r="DM63" t="n">
-        <v>0.6081479110085386</v>
+        <v>0.6081479110085387</v>
       </c>
       <c r="DN63" t="n">
         <v>0.5900214578269309</v>
@@ -24243,7 +23983,7 @@
         <v>0.501764638175365</v>
       </c>
       <c r="B64" t="n">
-        <v>0.8919897941219301</v>
+        <v>0.8919897941219302</v>
       </c>
       <c r="C64" t="n">
         <v>0.9231280026005112</v>
@@ -24252,7 +23992,7 @@
         <v>0.9171939037648944</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9649650832131362</v>
+        <v>0.9649650832131361</v>
       </c>
       <c r="F64" t="n">
         <v>0.6652938200875487</v>
@@ -24261,7 +24001,7 @@
         <v>0.4312286155677278</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3787372196031626</v>
+        <v>0.3787372196031627</v>
       </c>
       <c r="I64" t="n">
         <v>0.2117972311744096</v>
@@ -24279,7 +24019,7 @@
         <v>0.3207955290524136</v>
       </c>
       <c r="N64" t="n">
-        <v>0.4998144942962749</v>
+        <v>0.499814494296275</v>
       </c>
       <c r="O64" t="n">
         <v>0.4029677882151566</v>
@@ -24294,7 +24034,7 @@
         <v>0.3950792029258792</v>
       </c>
       <c r="S64" t="n">
-        <v>0.4436856770916958</v>
+        <v>0.4436856770916959</v>
       </c>
       <c r="T64" t="n">
         <v>0.2517115716380042</v>
@@ -24306,7 +24046,7 @@
         <v>0.2562679967849986</v>
       </c>
       <c r="W64" t="n">
-        <v>0.3193037976645493</v>
+        <v>0.3193037976645494</v>
       </c>
       <c r="X64" t="n">
         <v>0.3855662903679757</v>
@@ -24342,7 +24082,7 @@
         <v>0.4256606336058593</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.4798602693758393</v>
+        <v>0.4798602693758391</v>
       </c>
       <c r="AJ64" t="n">
         <v>0.3097327636974518</v>
@@ -24456,7 +24196,7 @@
         <v>0.2481129044282344</v>
       </c>
       <c r="BU64" t="n">
-        <v>0.4135612357892252</v>
+        <v>0.4135612357892251</v>
       </c>
       <c r="BV64" t="n">
         <v>0.2852234780217218</v>
@@ -24537,7 +24277,7 @@
         <v>0.3136647380366664</v>
       </c>
       <c r="CV64" t="n">
-        <v>0.4293383411647878</v>
+        <v>0.4293383411647879</v>
       </c>
       <c r="CW64" t="n">
         <v>0.3708590240459051</v>
@@ -24561,7 +24301,7 @@
         <v>0.354309265174358</v>
       </c>
       <c r="DD64" t="n">
-        <v>0.2782715369447002</v>
+        <v>0.2782715369447001</v>
       </c>
       <c r="DE64" t="n">
         <v>0.3278529693013087</v>
@@ -24620,7 +24360,7 @@
         <v>0.8947457767023256</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9200193083493422</v>
+        <v>0.9200193083493424</v>
       </c>
       <c r="D65" t="n">
         <v>0.9244828646079517</v>
@@ -24635,7 +24375,7 @@
         <v>0.3253999652994082</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2761990557088671</v>
+        <v>0.2761990557088672</v>
       </c>
       <c r="I65" t="n">
         <v>0.1372928074270492</v>
@@ -24692,7 +24432,7 @@
         <v>0.1685405556629931</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.3486168269176707</v>
+        <v>0.3486168269176705</v>
       </c>
       <c r="AB65" t="n">
         <v>0.1666474150330017</v>
@@ -24770,7 +24510,7 @@
         <v>0.3439911381169857</v>
       </c>
       <c r="BA65" t="n">
-        <v>0.04719005943363253</v>
+        <v>0.04719005943363252</v>
       </c>
       <c r="BB65" t="n">
         <v>0.2425355784730887</v>
@@ -24788,7 +24528,7 @@
         <v>0.3248706543140846</v>
       </c>
       <c r="BG65" t="n">
-        <v>0.2410910702881993</v>
+        <v>0.2410910702881992</v>
       </c>
       <c r="BH65" t="n">
         <v>0.694679960053306</v>
@@ -24800,7 +24540,7 @@
         <v>0.241187017772248</v>
       </c>
       <c r="BK65" t="n">
-        <v>0.3579599587876301</v>
+        <v>0.3579599587876302</v>
       </c>
       <c r="BL65" t="n">
         <v>0.302886408192353</v>
@@ -24896,7 +24636,7 @@
         <v>0.2129275248372388</v>
       </c>
       <c r="CQ65" t="n">
-        <v>0.2832240905014259</v>
+        <v>0.283224090501426</v>
       </c>
       <c r="CR65" t="n">
         <v>0.1926022157149125</v>
@@ -24962,7 +24702,7 @@
         <v>0.1877415824669345</v>
       </c>
       <c r="DM65" t="n">
-        <v>0.3859990298306512</v>
+        <v>0.3859990298306513</v>
       </c>
       <c r="DN65" t="n">
         <v>0.3706632013314958</v>
@@ -25033,7 +24773,7 @@
         <v>0.2029562682805878</v>
       </c>
       <c r="P66" t="n">
-        <v>0.03629352779123075</v>
+        <v>0.03629352779123074</v>
       </c>
       <c r="Q66" t="n">
         <v>0.2942041950881321</v>
@@ -25153,7 +24893,7 @@
         <v>0.1320690961142531</v>
       </c>
       <c r="BD66" t="n">
-        <v>0.2099351892604456</v>
+        <v>0.2099351892604455</v>
       </c>
       <c r="BE66" t="n">
         <v>0.07356519860423325</v>
@@ -25192,7 +24932,7 @@
         <v>0.1104390079968578</v>
       </c>
       <c r="BQ66" t="n">
-        <v>0.2163200022707946</v>
+        <v>0.2163200022707947</v>
       </c>
       <c r="BR66" t="n">
         <v>0.1443288689659793</v>
@@ -25330,7 +25070,7 @@
         <v>0.1189081883005068</v>
       </c>
       <c r="DK66" t="n">
-        <v>0.1913957787647687</v>
+        <v>0.1913957787647686</v>
       </c>
       <c r="DL66" t="n">
         <v>0.1153688984341128</v>
@@ -25536,7 +25276,7 @@
         <v>0.1411121498015588</v>
       </c>
       <c r="BG67" t="n">
-        <v>0.09130820417406503</v>
+        <v>0.09130820417406504</v>
       </c>
       <c r="BH67" t="n">
         <v>0.623079118860822</v>
@@ -25563,7 +25303,7 @@
         <v>0.1495820794983151</v>
       </c>
       <c r="BP67" t="n">
-        <v>0.06079872166738559</v>
+        <v>0.06079872166738558</v>
       </c>
       <c r="BQ67" t="n">
         <v>0.1351799179179719</v>
@@ -25581,7 +25321,7 @@
         <v>0.1401232429670285</v>
       </c>
       <c r="BV67" t="n">
-        <v>0.06097752988718538</v>
+        <v>0.06097752988718539</v>
       </c>
       <c r="BW67" t="n">
         <v>0.07732861979321251</v>
@@ -25599,7 +25339,7 @@
         <v>0.03807639667400849</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.08796172213683875</v>
+        <v>0.08796172213683874</v>
       </c>
       <c r="CC67" t="n">
         <v>0.1333240677839665</v>
@@ -25617,7 +25357,7 @@
         <v>0.1472847743200991</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.04196502165952174</v>
+        <v>0.04196502165952175</v>
       </c>
       <c r="CI67" t="n">
         <v>0.09458348968031967</v>
@@ -25638,7 +25378,7 @@
         <v>0.1120273290431808</v>
       </c>
       <c r="CO67" t="n">
-        <v>0.05473446380812046</v>
+        <v>0.05473446380812044</v>
       </c>
       <c r="CP67" t="n">
         <v>0.07672103920850533</v>
@@ -25671,7 +25411,7 @@
         <v>0.03624798357415573</v>
       </c>
       <c r="CZ67" t="n">
-        <v>0.08911518839565256</v>
+        <v>0.08911518839565259</v>
       </c>
       <c r="DA67" t="n">
         <v>0.1666859409556049</v>
@@ -25719,7 +25459,7 @@
         <v>0.05347972837697747</v>
       </c>
       <c r="DP67" t="n">
-        <v>0.4837742760302783</v>
+        <v>0.4837742760302782</v>
       </c>
       <c r="DQ67" t="n">
         <v>0.7819170221094992</v>
@@ -25742,13 +25482,13 @@
         <v>0.8971725261116067</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8926304653016121</v>
+        <v>0.8926304653016119</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9312246134326327</v>
+        <v>0.9312246134326326</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8301208462316284</v>
+        <v>0.8301208462316285</v>
       </c>
       <c r="F68" t="n">
         <v>0.2818158262972741</v>
@@ -25763,10 +25503,10 @@
         <v>0.02803782730133036</v>
       </c>
       <c r="J68" t="n">
-        <v>0.09096094216598484</v>
+        <v>0.09096094216598487</v>
       </c>
       <c r="K68" t="n">
-        <v>0.08401169220443711</v>
+        <v>0.08401169220443709</v>
       </c>
       <c r="L68" t="n">
         <v>0.16307630058481</v>
@@ -25805,7 +25545,7 @@
         <v>0.04831101071240636</v>
       </c>
       <c r="X68" t="n">
-        <v>0.06198301500123588</v>
+        <v>0.06198301500123587</v>
       </c>
       <c r="Y68" t="n">
         <v>0.06421252230474972</v>
@@ -25814,7 +25554,7 @@
         <v>0.03128687389172855</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.1031648146110365</v>
+        <v>0.1031648146110366</v>
       </c>
       <c r="AB68" t="n">
         <v>0.02902790347319293</v>
@@ -25832,7 +25572,7 @@
         <v>0.1047605449577745</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.03037864720285754</v>
+        <v>0.03037864720285755</v>
       </c>
       <c r="AH68" t="n">
         <v>0.09723893851309537</v>
@@ -25856,7 +25596,7 @@
         <v>0.1424039800121967</v>
       </c>
       <c r="AO68" t="n">
-        <v>0.04976014636839935</v>
+        <v>0.04976014636839934</v>
       </c>
       <c r="AP68" t="n">
         <v>0.03911698322915484</v>
@@ -25880,7 +25620,7 @@
         <v>0.02822256181308787</v>
       </c>
       <c r="AW68" t="n">
-        <v>0.140165401254724</v>
+        <v>0.1401654012547241</v>
       </c>
       <c r="AX68" t="n">
         <v>0.2175211004302314</v>
@@ -25934,7 +25674,7 @@
         <v>0.03455859469055159</v>
       </c>
       <c r="BO68" t="n">
-        <v>0.08757272513177616</v>
+        <v>0.08757272513177615</v>
       </c>
       <c r="BP68" t="n">
         <v>0.03161414580936118</v>
@@ -25949,7 +25689,7 @@
         <v>0.02226314813742955</v>
       </c>
       <c r="BT68" t="n">
-        <v>0.02672827139206579</v>
+        <v>0.02672827139206578</v>
       </c>
       <c r="BU68" t="n">
         <v>0.08493199300233846</v>
@@ -25991,13 +25731,13 @@
         <v>0.08738505376974133</v>
       </c>
       <c r="CH68" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI68" t="n">
         <v>0.05068323568994176</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.06834167433025466</v>
+        <v>0.06834167433025465</v>
       </c>
       <c r="CK68" t="n">
         <v>0.05791660307631274</v>
@@ -26179,7 +25919,7 @@
         <v>0.02641626556209874</v>
       </c>
       <c r="X69" t="n">
-        <v>0.03210743847815197</v>
+        <v>0.03210743847815196</v>
       </c>
       <c r="Y69" t="n">
         <v>0.03641672105135444</v>
@@ -26209,7 +25949,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI69" t="n">
         <v>0.08191683659879095</v>
@@ -26341,7 +26081,7 @@
         <v>0.02207522206080373</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0.03303420867610114</v>
+        <v>0.03303420867610115</v>
       </c>
       <c r="CA69" t="n">
         <v>0.01907208991009711</v>
@@ -26365,7 +26105,7 @@
         <v>0.04786652496108034</v>
       </c>
       <c r="CH69" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI69" t="n">
         <v>0.02564326647040785</v>
@@ -26383,7 +26123,7 @@
         <v>0.05891630846307996</v>
       </c>
       <c r="CN69" t="n">
-        <v>0.03106300969466722</v>
+        <v>0.03106300969466723</v>
       </c>
       <c r="CO69" t="n">
         <v>0.01699268019259806</v>
@@ -26452,7 +26192,7 @@
         <v>0.01846360144730119</v>
       </c>
       <c r="DK69" t="n">
-        <v>0.04102384732649984</v>
+        <v>0.04102384732649985</v>
       </c>
       <c r="DL69" t="n">
         <v>0.01806833879855582</v>
@@ -26479,7 +26219,7 @@
         <v>0.8741825756236765</v>
       </c>
       <c r="DT69" t="n">
-        <v>0.8904460955569445</v>
+        <v>0.8904460955569444</v>
       </c>
     </row>
     <row r="70">
@@ -26520,7 +26260,7 @@
         <v>0.05732953913859099</v>
       </c>
       <c r="M70" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N70" t="n">
         <v>0.0397778622716073</v>
@@ -26535,7 +26275,7 @@
         <v>0.04160321852019425</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S70" t="n">
         <v>0.0318052040632217</v>
@@ -26583,7 +26323,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI70" t="n">
         <v>0.05479109437005748</v>
@@ -26655,7 +26395,7 @@
         <v>0.01834704020788646</v>
       </c>
       <c r="BF70" t="n">
-        <v>0.02299367216459849</v>
+        <v>0.02299367216459848</v>
       </c>
       <c r="BG70" t="n">
         <v>0.0144384409874184</v>
@@ -26700,7 +26440,7 @@
         <v>0.01619053209296189</v>
       </c>
       <c r="BU70" t="n">
-        <v>0.02785646149769065</v>
+        <v>0.02785646149769064</v>
       </c>
       <c r="BV70" t="n">
         <v>0.01672194888722292</v>
@@ -26739,7 +26479,7 @@
         <v>0.02529651442184988</v>
       </c>
       <c r="CH70" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI70" t="n">
         <v>0.01398835324507469</v>
@@ -26763,7 +26503,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP70" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ70" t="n">
         <v>0.01854170128619982</v>
@@ -26796,7 +26536,7 @@
         <v>0.01452630766475907</v>
       </c>
       <c r="DA70" t="n">
-        <v>0.0339053683529906</v>
+        <v>0.03390536835299061</v>
       </c>
       <c r="DB70" t="n">
         <v>0.017944027643374</v>
@@ -26847,7 +26587,7 @@
         <v>0.593905711432783</v>
       </c>
       <c r="DR70" t="n">
-        <v>0.6062877341534579</v>
+        <v>0.606287734153458</v>
       </c>
       <c r="DS70" t="n">
         <v>0.8697367139530003</v>
@@ -26894,7 +26634,7 @@
         <v>0.03008903030839145</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N71" t="n">
         <v>0.02207938408527719</v>
@@ -26909,7 +26649,7 @@
         <v>0.0233455845392363</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S71" t="n">
         <v>0.01965569383968971</v>
@@ -26957,7 +26697,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI71" t="n">
         <v>0.05479109437005748</v>
@@ -27113,7 +26853,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH71" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI71" t="n">
         <v>0.01398835324507469</v>
@@ -27137,7 +26877,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP71" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ71" t="n">
         <v>0.01854170128619982</v>
@@ -27268,7 +27008,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M72" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N72" t="n">
         <v>0.0138419432176799</v>
@@ -27283,7 +27023,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S72" t="n">
         <v>0.01321664211486768</v>
@@ -27331,7 +27071,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI72" t="n">
         <v>0.05479109437005748</v>
@@ -27487,7 +27227,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH72" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI72" t="n">
         <v>0.01398835324507469</v>
@@ -27511,7 +27251,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP72" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ72" t="n">
         <v>0.01854170128619982</v>
@@ -27618,7 +27358,7 @@
         <v>0.8511173152743188</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4366198664915349</v>
+        <v>0.4366198664915348</v>
       </c>
       <c r="F73" t="n">
         <v>0.02360563657727953</v>
@@ -27642,7 +27382,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M73" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N73" t="n">
         <v>0.0138419432176799</v>
@@ -27657,7 +27397,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R73" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S73" t="n">
         <v>0.01321664211486768</v>
@@ -27705,7 +27445,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI73" t="n">
         <v>0.05479109437005748</v>
@@ -27861,7 +27601,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI73" t="n">
         <v>0.01398835324507469</v>
@@ -27885,7 +27625,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP73" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ73" t="n">
         <v>0.01854170128619982</v>
@@ -27980,7 +27720,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.1806328909574811</v>
+        <v>0.180632890957481</v>
       </c>
       <c r="B74" t="n">
         <v>0.8933518129928738</v>
@@ -28016,7 +27756,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M74" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N74" t="n">
         <v>0.0138419432176799</v>
@@ -28031,7 +27771,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R74" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S74" t="n">
         <v>0.01321664211486768</v>
@@ -28079,7 +27819,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI74" t="n">
         <v>0.05479109437005748</v>
@@ -28235,7 +27975,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH74" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI74" t="n">
         <v>0.01398835324507469</v>
@@ -28259,7 +27999,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP74" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ74" t="n">
         <v>0.01854170128619982</v>
@@ -28390,7 +28130,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M75" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N75" t="n">
         <v>0.0138419432176799</v>
@@ -28405,7 +28145,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R75" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S75" t="n">
         <v>0.01321664211486768</v>
@@ -28453,7 +28193,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI75" t="n">
         <v>0.05479109437005748</v>
@@ -28609,7 +28349,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH75" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI75" t="n">
         <v>0.01398835324507469</v>
@@ -28633,7 +28373,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP75" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ75" t="n">
         <v>0.01854170128619982</v>
@@ -28764,7 +28504,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N76" t="n">
         <v>0.0138419432176799</v>
@@ -28779,7 +28519,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S76" t="n">
         <v>0.01321664211486768</v>
@@ -28827,7 +28567,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI76" t="n">
         <v>0.05479109437005748</v>
@@ -28983,7 +28723,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH76" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI76" t="n">
         <v>0.01398835324507469</v>
@@ -29007,7 +28747,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP76" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ76" t="n">
         <v>0.01854170128619982</v>
@@ -29097,7 +28837,7 @@
         <v>0.8527539785643447</v>
       </c>
       <c r="DT76" t="n">
-        <v>0.8202639290805313</v>
+        <v>0.8202639290805314</v>
       </c>
     </row>
     <row r="77">
@@ -29138,7 +28878,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N77" t="n">
         <v>0.0138419432176799</v>
@@ -29153,7 +28893,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S77" t="n">
         <v>0.01321664211486768</v>
@@ -29201,7 +28941,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI77" t="n">
         <v>0.05479109437005748</v>
@@ -29282,7 +29022,7 @@
         <v>0.4298291535404298</v>
       </c>
       <c r="BI77" t="n">
-        <v>0.07722545314023722</v>
+        <v>0.07722545314023721</v>
       </c>
       <c r="BJ77" t="n">
         <v>0.01462818892870313</v>
@@ -29357,7 +29097,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH77" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI77" t="n">
         <v>0.01398835324507469</v>
@@ -29381,7 +29121,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP77" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ77" t="n">
         <v>0.01854170128619982</v>
@@ -29462,7 +29202,7 @@
         <v>0.01851807909027293</v>
       </c>
       <c r="DQ77" t="n">
-        <v>0.09046081605868261</v>
+        <v>0.09046081605868259</v>
       </c>
       <c r="DR77" t="n">
         <v>0.5379024085740031</v>
@@ -29512,7 +29252,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M78" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N78" t="n">
         <v>0.0138419432176799</v>
@@ -29527,7 +29267,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S78" t="n">
         <v>0.01321664211486768</v>
@@ -29575,7 +29315,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI78" t="n">
         <v>0.05479109437005748</v>
@@ -29731,7 +29471,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH78" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI78" t="n">
         <v>0.01398835324507469</v>
@@ -29755,7 +29495,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP78" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ78" t="n">
         <v>0.01854170128619982</v>
@@ -29886,7 +29626,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M79" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N79" t="n">
         <v>0.0138419432176799</v>
@@ -29901,7 +29641,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S79" t="n">
         <v>0.01321664211486768</v>
@@ -29949,7 +29689,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI79" t="n">
         <v>0.05479109437005748</v>
@@ -30027,7 +29767,7 @@
         <v>0.0144384409874184</v>
       </c>
       <c r="BH79" t="n">
-        <v>0.402339228783391</v>
+        <v>0.4023392287833909</v>
       </c>
       <c r="BI79" t="n">
         <v>0.02454661965811045</v>
@@ -30105,7 +29845,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI79" t="n">
         <v>0.01398835324507469</v>
@@ -30129,7 +29869,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP79" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ79" t="n">
         <v>0.01854170128619982</v>
@@ -30260,7 +30000,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M80" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N80" t="n">
         <v>0.0138419432176799</v>
@@ -30275,7 +30015,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S80" t="n">
         <v>0.01321664211486768</v>
@@ -30323,7 +30063,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI80" t="n">
         <v>0.05479109437005748</v>
@@ -30479,7 +30219,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH80" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI80" t="n">
         <v>0.01398835324507469</v>
@@ -30503,7 +30243,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP80" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ80" t="n">
         <v>0.01854170128619982</v>
@@ -30604,7 +30344,7 @@
         <v>0.8908375471039384</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3900867102688829</v>
+        <v>0.3900867102688828</v>
       </c>
       <c r="D81" t="n">
         <v>0.4422922484035222</v>
@@ -30634,7 +30374,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N81" t="n">
         <v>0.0138419432176799</v>
@@ -30649,7 +30389,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S81" t="n">
         <v>0.01321664211486768</v>
@@ -30697,7 +30437,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI81" t="n">
         <v>0.05479109437005748</v>
@@ -30853,7 +30593,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH81" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI81" t="n">
         <v>0.01398835324507469</v>
@@ -30877,7 +30617,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP81" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ81" t="n">
         <v>0.01854170128619982</v>
@@ -30964,7 +30704,7 @@
         <v>0.5082843435825023</v>
       </c>
       <c r="DS81" t="n">
-        <v>0.7970515563231563</v>
+        <v>0.7970515563231564</v>
       </c>
       <c r="DT81" t="n">
         <v>0.6802304167483063</v>
@@ -31008,7 +30748,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M82" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N82" t="n">
         <v>0.0138419432176799</v>
@@ -31023,7 +30763,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S82" t="n">
         <v>0.01321664211486768</v>
@@ -31071,7 +30811,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI82" t="n">
         <v>0.05479109437005748</v>
@@ -31227,7 +30967,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI82" t="n">
         <v>0.01398835324507469</v>
@@ -31251,7 +30991,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP82" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ82" t="n">
         <v>0.01854170128619982</v>
@@ -31382,7 +31122,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M83" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N83" t="n">
         <v>0.0138419432176799</v>
@@ -31397,7 +31137,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S83" t="n">
         <v>0.01321664211486768</v>
@@ -31445,7 +31185,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI83" t="n">
         <v>0.05479109437005748</v>
@@ -31601,7 +31341,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI83" t="n">
         <v>0.01398835324507469</v>
@@ -31625,7 +31365,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP83" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ83" t="n">
         <v>0.01854170128619982</v>
@@ -31756,7 +31496,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M84" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N84" t="n">
         <v>0.0138419432176799</v>
@@ -31771,7 +31511,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S84" t="n">
         <v>0.01321664211486768</v>
@@ -31819,7 +31559,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI84" t="n">
         <v>0.05479109437005748</v>
@@ -31975,7 +31715,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH84" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI84" t="n">
         <v>0.01398835324507469</v>
@@ -31999,7 +31739,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP84" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ84" t="n">
         <v>0.01854170128619982</v>
@@ -32130,7 +31870,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M85" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N85" t="n">
         <v>0.0138419432176799</v>
@@ -32145,7 +31885,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S85" t="n">
         <v>0.01321664211486768</v>
@@ -32193,7 +31933,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI85" t="n">
         <v>0.05479109437005748</v>
@@ -32349,7 +32089,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH85" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI85" t="n">
         <v>0.01398835324507469</v>
@@ -32373,7 +32113,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP85" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ85" t="n">
         <v>0.01854170128619982</v>
@@ -32504,7 +32244,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M86" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N86" t="n">
         <v>0.0138419432176799</v>
@@ -32519,7 +32259,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S86" t="n">
         <v>0.01321664211486768</v>
@@ -32567,7 +32307,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI86" t="n">
         <v>0.05479109437005748</v>
@@ -32723,7 +32463,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH86" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI86" t="n">
         <v>0.01398835324507469</v>
@@ -32747,7 +32487,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP86" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ86" t="n">
         <v>0.01854170128619982</v>
@@ -32848,7 +32588,7 @@
         <v>0.7990353382896604</v>
       </c>
       <c r="C87" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D87" t="n">
         <v>0.0869940603555717</v>
@@ -32878,7 +32618,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M87" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N87" t="n">
         <v>0.0138419432176799</v>
@@ -32893,7 +32633,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R87" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S87" t="n">
         <v>0.01321664211486768</v>
@@ -32941,7 +32681,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH87" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI87" t="n">
         <v>0.05479109437005748</v>
@@ -33097,7 +32837,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH87" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI87" t="n">
         <v>0.01398835324507469</v>
@@ -33121,7 +32861,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP87" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ87" t="n">
         <v>0.01854170128619982</v>
@@ -33222,7 +32962,7 @@
         <v>0.7747240608393819</v>
       </c>
       <c r="C88" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D88" t="n">
         <v>0.06000349015010351</v>
@@ -33252,7 +32992,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M88" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N88" t="n">
         <v>0.0138419432176799</v>
@@ -33267,7 +33007,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S88" t="n">
         <v>0.01321664211486768</v>
@@ -33315,7 +33055,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI88" t="n">
         <v>0.05479109437005748</v>
@@ -33471,7 +33211,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI88" t="n">
         <v>0.01398835324507469</v>
@@ -33495,7 +33235,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP88" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ88" t="n">
         <v>0.01854170128619982</v>
@@ -33596,7 +33336,7 @@
         <v>0.7481306800550898</v>
       </c>
       <c r="C89" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D89" t="n">
         <v>0.06000349015010351</v>
@@ -33626,7 +33366,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M89" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N89" t="n">
         <v>0.0138419432176799</v>
@@ -33641,7 +33381,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S89" t="n">
         <v>0.01321664211486768</v>
@@ -33689,7 +33429,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI89" t="n">
         <v>0.05479109437005748</v>
@@ -33845,7 +33585,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH89" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI89" t="n">
         <v>0.01398835324507469</v>
@@ -33869,7 +33609,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP89" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ89" t="n">
         <v>0.01854170128619982</v>
@@ -33967,10 +33707,10 @@
         <v>0.01688699225356498</v>
       </c>
       <c r="B90" t="n">
-        <v>0.7198260460082837</v>
+        <v>0.7198260460082836</v>
       </c>
       <c r="C90" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D90" t="n">
         <v>0.06000349015010351</v>
@@ -34000,7 +33740,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M90" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N90" t="n">
         <v>0.0138419432176799</v>
@@ -34015,7 +33755,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S90" t="n">
         <v>0.01321664211486768</v>
@@ -34063,7 +33803,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI90" t="n">
         <v>0.05479109437005748</v>
@@ -34219,7 +33959,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH90" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI90" t="n">
         <v>0.01398835324507469</v>
@@ -34243,7 +33983,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP90" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ90" t="n">
         <v>0.01854170128619982</v>
@@ -34344,7 +34084,7 @@
         <v>0.6906732532430584</v>
       </c>
       <c r="C91" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D91" t="n">
         <v>0.06000349015010351</v>
@@ -34374,7 +34114,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M91" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N91" t="n">
         <v>0.0138419432176799</v>
@@ -34389,7 +34129,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R91" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S91" t="n">
         <v>0.01321664211486768</v>
@@ -34437,7 +34177,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI91" t="n">
         <v>0.05479109437005748</v>
@@ -34593,7 +34333,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI91" t="n">
         <v>0.01398835324507469</v>
@@ -34617,7 +34357,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP91" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ91" t="n">
         <v>0.01854170128619982</v>
@@ -34718,7 +34458,7 @@
         <v>0.6615793426630308</v>
       </c>
       <c r="C92" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D92" t="n">
         <v>0.06000349015010351</v>
@@ -34748,7 +34488,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M92" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N92" t="n">
         <v>0.0138419432176799</v>
@@ -34763,7 +34503,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S92" t="n">
         <v>0.01321664211486768</v>
@@ -34811,7 +34551,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI92" t="n">
         <v>0.05479109437005748</v>
@@ -34967,7 +34707,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH92" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI92" t="n">
         <v>0.01398835324507469</v>
@@ -34991,7 +34731,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP92" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ92" t="n">
         <v>0.01854170128619982</v>
@@ -35092,7 +34832,7 @@
         <v>0.6332190639327554</v>
       </c>
       <c r="C93" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D93" t="n">
         <v>0.06000349015010351</v>
@@ -35122,7 +34862,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M93" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N93" t="n">
         <v>0.0138419432176799</v>
@@ -35137,7 +34877,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R93" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S93" t="n">
         <v>0.01321664211486768</v>
@@ -35185,7 +34925,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI93" t="n">
         <v>0.05479109437005748</v>
@@ -35341,7 +35081,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH93" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI93" t="n">
         <v>0.01398835324507469</v>
@@ -35365,7 +35105,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP93" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ93" t="n">
         <v>0.01854170128619982</v>
@@ -35466,7 +35206,7 @@
         <v>0.6059310772511142</v>
       </c>
       <c r="C94" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D94" t="n">
         <v>0.06000349015010351</v>
@@ -35496,7 +35236,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M94" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N94" t="n">
         <v>0.0138419432176799</v>
@@ -35511,7 +35251,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S94" t="n">
         <v>0.01321664211486768</v>
@@ -35559,7 +35299,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI94" t="n">
         <v>0.05479109437005748</v>
@@ -35715,7 +35455,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH94" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI94" t="n">
         <v>0.01398835324507469</v>
@@ -35739,7 +35479,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP94" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ94" t="n">
         <v>0.01854170128619982</v>
@@ -35840,7 +35580,7 @@
         <v>0.5797579663248684</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D95" t="n">
         <v>0.06000349015010351</v>
@@ -35870,7 +35610,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M95" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N95" t="n">
         <v>0.0138419432176799</v>
@@ -35885,7 +35625,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R95" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S95" t="n">
         <v>0.01321664211486768</v>
@@ -35933,7 +35673,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI95" t="n">
         <v>0.05479109437005748</v>
@@ -36089,7 +35829,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH95" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI95" t="n">
         <v>0.01398835324507469</v>
@@ -36113,7 +35853,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP95" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ95" t="n">
         <v>0.01854170128619982</v>
@@ -36214,7 +35954,7 @@
         <v>0.5545460751326973</v>
       </c>
       <c r="C96" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D96" t="n">
         <v>0.06000349015010351</v>
@@ -36244,7 +35984,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M96" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N96" t="n">
         <v>0.0138419432176799</v>
@@ -36259,7 +35999,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R96" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S96" t="n">
         <v>0.01321664211486768</v>
@@ -36307,7 +36047,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI96" t="n">
         <v>0.05479109437005748</v>
@@ -36463,7 +36203,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH96" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI96" t="n">
         <v>0.01398835324507469</v>
@@ -36487,7 +36227,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP96" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ96" t="n">
         <v>0.01854170128619982</v>
@@ -36588,7 +36328,7 @@
         <v>0.5300823256160175</v>
       </c>
       <c r="C97" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D97" t="n">
         <v>0.06000349015010351</v>
@@ -36618,7 +36358,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M97" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N97" t="n">
         <v>0.0138419432176799</v>
@@ -36633,7 +36373,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R97" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S97" t="n">
         <v>0.01321664211486768</v>
@@ -36681,7 +36421,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI97" t="n">
         <v>0.05479109437005748</v>
@@ -36837,7 +36577,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH97" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI97" t="n">
         <v>0.01398835324507469</v>
@@ -36861,7 +36601,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP97" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ97" t="n">
         <v>0.01854170128619982</v>
@@ -36962,7 +36702,7 @@
         <v>0.5061799541600034</v>
       </c>
       <c r="C98" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D98" t="n">
         <v>0.06000349015010351</v>
@@ -36992,7 +36732,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M98" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N98" t="n">
         <v>0.0138419432176799</v>
@@ -37007,7 +36747,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R98" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S98" t="n">
         <v>0.01321664211486768</v>
@@ -37055,7 +36795,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI98" t="n">
         <v>0.05479109437005748</v>
@@ -37211,7 +36951,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH98" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI98" t="n">
         <v>0.01398835324507469</v>
@@ -37235,7 +36975,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP98" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ98" t="n">
         <v>0.01854170128619982</v>
@@ -37336,7 +37076,7 @@
         <v>0.4826522699257159</v>
       </c>
       <c r="C99" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D99" t="n">
         <v>0.06000349015010351</v>
@@ -37366,7 +37106,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M99" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N99" t="n">
         <v>0.0138419432176799</v>
@@ -37381,7 +37121,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R99" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S99" t="n">
         <v>0.01321664211486768</v>
@@ -37429,7 +37169,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH99" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI99" t="n">
         <v>0.05479109437005748</v>
@@ -37585,7 +37325,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH99" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI99" t="n">
         <v>0.01398835324507469</v>
@@ -37609,7 +37349,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP99" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ99" t="n">
         <v>0.01854170128619982</v>
@@ -37699,7 +37439,7 @@
         <v>0.05066976978865074</v>
       </c>
       <c r="DT99" t="n">
-        <v>0.05897102646486103</v>
+        <v>0.05897102646486102</v>
       </c>
     </row>
     <row r="100">
@@ -37710,7 +37450,7 @@
         <v>0.4592511723525005</v>
       </c>
       <c r="C100" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D100" t="n">
         <v>0.06000349015010351</v>
@@ -37740,7 +37480,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M100" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N100" t="n">
         <v>0.0138419432176799</v>
@@ -37755,7 +37495,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S100" t="n">
         <v>0.01321664211486768</v>
@@ -37803,7 +37543,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH100" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI100" t="n">
         <v>0.05479109437005748</v>
@@ -37959,7 +37699,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH100" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI100" t="n">
         <v>0.01398835324507469</v>
@@ -37983,7 +37723,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP100" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ100" t="n">
         <v>0.01854170128619982</v>
@@ -38073,7 +37813,7 @@
         <v>0.05066976978865074</v>
       </c>
       <c r="DT100" t="n">
-        <v>0.05897102646486103</v>
+        <v>0.05897102646486102</v>
       </c>
     </row>
     <row r="101">
@@ -38084,7 +37824,7 @@
         <v>0.4356414033726229</v>
       </c>
       <c r="C101" t="n">
-        <v>0.06692124888132094</v>
+        <v>0.06692124888132095</v>
       </c>
       <c r="D101" t="n">
         <v>0.06000349015010351</v>
@@ -38114,7 +37854,7 @@
         <v>0.01574150256163689</v>
       </c>
       <c r="M101" t="n">
-        <v>0.01380067808638435</v>
+        <v>0.01380067808638434</v>
       </c>
       <c r="N101" t="n">
         <v>0.0138419432176799</v>
@@ -38129,7 +37869,7 @@
         <v>0.01471894560072796</v>
       </c>
       <c r="R101" t="n">
-        <v>0.01912634203069817</v>
+        <v>0.01912634203069818</v>
       </c>
       <c r="S101" t="n">
         <v>0.01321664211486768</v>
@@ -38177,7 +37917,7 @@
         <v>0.01707154914659288</v>
       </c>
       <c r="AH101" t="n">
-        <v>0.05895520379020459</v>
+        <v>0.05895520379020458</v>
       </c>
       <c r="AI101" t="n">
         <v>0.05479109437005748</v>
@@ -38333,7 +38073,7 @@
         <v>0.01445288404891794</v>
       </c>
       <c r="CH101" t="n">
-        <v>0.02067812131260747</v>
+        <v>0.02067812131260746</v>
       </c>
       <c r="CI101" t="n">
         <v>0.01398835324507469</v>
@@ -38357,7 +38097,7 @@
         <v>0.01699268019259806</v>
       </c>
       <c r="CP101" t="n">
-        <v>0.01512094504460756</v>
+        <v>0.01512094504460755</v>
       </c>
       <c r="CQ101" t="n">
         <v>0.01854170128619982</v>
@@ -38447,7 +38187,7 @@
         <v>0.05066976978865074</v>
       </c>
       <c r="DT101" t="n">
-        <v>0.05897102646486103</v>
+        <v>0.05897102646486102</v>
       </c>
     </row>
   </sheetData>
